--- a/base_cenarios_rs.xlsx
+++ b/base_cenarios_rs.xlsx
@@ -417,13 +417,13 @@
         <v>2.312890552967748</v>
       </c>
       <c r="F2">
-        <v>197.49</v>
+        <v>133.29</v>
       </c>
       <c r="G2">
-        <v>301</v>
+        <v>87.73</v>
       </c>
       <c r="H2">
-        <v>302.77</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="3">
@@ -447,13 +447,13 @@
         <v>4.212820929444834</v>
       </c>
       <c r="F3">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G3">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H3">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -477,13 +477,13 @@
         <v>6.016094250716584</v>
       </c>
       <c r="F4">
-        <v>214.5</v>
+        <v>158.02</v>
       </c>
       <c r="G4">
-        <v>206.18</v>
+        <v>49.15</v>
       </c>
       <c r="H4">
-        <v>196.04</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="5">
@@ -507,13 +507,13 @@
         <v>7.667290115051093</v>
       </c>
       <c r="F5">
-        <v>239.71</v>
+        <v>152.73</v>
       </c>
       <c r="G5">
-        <v>322.66</v>
+        <v>115.24</v>
       </c>
       <c r="H5">
-        <v>299.66</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="6">
@@ -537,13 +537,13 @@
         <v>9.313363224648736</v>
       </c>
       <c r="F6">
-        <v>175.84</v>
+        <v>129.29</v>
       </c>
       <c r="G6">
-        <v>265.48</v>
+        <v>66.03999999999999</v>
       </c>
       <c r="H6">
-        <v>278.93</v>
+        <v>64.32000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -567,13 +567,13 @@
         <v>10.89456748050385</v>
       </c>
       <c r="F7">
-        <v>181.53</v>
+        <v>135.49</v>
       </c>
       <c r="G7">
-        <v>206.63</v>
+        <v>37.99</v>
       </c>
       <c r="H7">
-        <v>208.06</v>
+        <v>72.79000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -597,13 +597,13 @@
         <v>12.41541815779374</v>
       </c>
       <c r="F8">
-        <v>160.52</v>
+        <v>113.96</v>
       </c>
       <c r="G8">
-        <v>254.62</v>
+        <v>57.24</v>
       </c>
       <c r="H8">
-        <v>251.13</v>
+        <v>66.70999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -627,13 +627,13 @@
         <v>13.87396966139145</v>
       </c>
       <c r="F9">
-        <v>234.86</v>
+        <v>149.59</v>
       </c>
       <c r="G9">
-        <v>299.05</v>
+        <v>136.37</v>
       </c>
       <c r="H9">
-        <v>240.52</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="10">
@@ -657,13 +657,13 @@
         <v>15.14025319249882</v>
       </c>
       <c r="F10">
-        <v>293.58</v>
+        <v>150.62</v>
       </c>
       <c r="G10">
-        <v>316.07</v>
+        <v>151.76</v>
       </c>
       <c r="H10">
-        <v>223.42</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="11">
@@ -687,13 +687,13 @@
         <v>16.36361185814492</v>
       </c>
       <c r="F11">
-        <v>271.67</v>
+        <v>147.56</v>
       </c>
       <c r="G11">
-        <v>308.19</v>
+        <v>170.14</v>
       </c>
       <c r="H11">
-        <v>197.49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -717,13 +717,13 @@
         <v>17.4805356768594</v>
       </c>
       <c r="F12">
-        <v>178.67</v>
+        <v>116.13</v>
       </c>
       <c r="G12">
-        <v>264.7</v>
+        <v>85</v>
       </c>
       <c r="H12">
-        <v>233.92</v>
+        <v>79.73999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -747,13 +747,13 @@
         <v>18.55681233251588</v>
       </c>
       <c r="F13">
-        <v>197.58</v>
+        <v>130.4</v>
       </c>
       <c r="G13">
-        <v>297.24</v>
+        <v>78.57000000000001</v>
       </c>
       <c r="H13">
-        <v>320.91</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="14">
@@ -777,13 +777,13 @@
         <v>19.61132073999147</v>
       </c>
       <c r="F14">
-        <v>228.98</v>
+        <v>168.32</v>
       </c>
       <c r="G14">
-        <v>291.58</v>
+        <v>115.17</v>
       </c>
       <c r="H14">
-        <v>236.66</v>
+        <v>66.23</v>
       </c>
     </row>
     <row r="15">
@@ -807,13 +807,13 @@
         <v>20.58203156275598</v>
       </c>
       <c r="F15">
-        <v>259.4</v>
+        <v>154.63</v>
       </c>
       <c r="G15">
-        <v>287.6</v>
+        <v>160.89</v>
       </c>
       <c r="H15">
-        <v>183.21</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="16">
@@ -837,13 +837,13 @@
         <v>21.54059832945059</v>
       </c>
       <c r="F16">
-        <v>261.55</v>
+        <v>181.8</v>
       </c>
       <c r="G16">
-        <v>312.36</v>
+        <v>129.63</v>
       </c>
       <c r="H16">
-        <v>262.78</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="17">
@@ -867,13 +867,13 @@
         <v>22.46491653327717</v>
       </c>
       <c r="F17">
-        <v>236.36</v>
+        <v>156.53</v>
       </c>
       <c r="G17">
-        <v>315.85</v>
+        <v>108.62</v>
       </c>
       <c r="H17">
-        <v>299.02</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="18">
@@ -897,13 +897,13 @@
         <v>23.383054774204</v>
       </c>
       <c r="F18">
-        <v>232.88</v>
+        <v>169.13</v>
       </c>
       <c r="G18">
-        <v>226.37</v>
+        <v>98.88</v>
       </c>
       <c r="H18">
-        <v>215.68</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="19">
@@ -927,13 +927,13 @@
         <v>24.27313410162477</v>
       </c>
       <c r="F19">
-        <v>169</v>
+        <v>126.02</v>
       </c>
       <c r="G19">
-        <v>233.76</v>
+        <v>49.33</v>
       </c>
       <c r="H19">
-        <v>241.4</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="20">
@@ -957,13 +957,13 @@
         <v>25.11944999271163</v>
       </c>
       <c r="F20">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G20">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H20">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="21">
@@ -987,13 +987,13 @@
         <v>25.96076075038864</v>
       </c>
       <c r="F21">
-        <v>220.96</v>
+        <v>141.04</v>
       </c>
       <c r="G21">
-        <v>263.36</v>
+        <v>77.72</v>
       </c>
       <c r="H21">
-        <v>225.98</v>
+        <v>113.83</v>
       </c>
     </row>
     <row r="22">
@@ -1017,13 +1017,13 @@
         <v>26.79102894112881</v>
       </c>
       <c r="F22">
-        <v>215.72</v>
+        <v>156.65</v>
       </c>
       <c r="G22">
-        <v>166.9</v>
+        <v>84.74000000000001</v>
       </c>
       <c r="H22">
-        <v>159.66</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="23">
@@ -1047,13 +1047,13 @@
         <v>27.61341511917822</v>
       </c>
       <c r="F23">
-        <v>188.1</v>
+        <v>124.25</v>
       </c>
       <c r="G23">
-        <v>274.87</v>
+        <v>104.93</v>
       </c>
       <c r="H23">
-        <v>234.11</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="24">
@@ -1077,13 +1077,13 @@
         <v>28.43561863822566</v>
       </c>
       <c r="F24">
-        <v>169</v>
+        <v>126.02</v>
       </c>
       <c r="G24">
-        <v>233.76</v>
+        <v>49.33</v>
       </c>
       <c r="H24">
-        <v>241.4</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="25">
@@ -1107,13 +1107,13 @@
         <v>29.22974248706228</v>
       </c>
       <c r="F25">
-        <v>234.86</v>
+        <v>149.59</v>
       </c>
       <c r="G25">
-        <v>299.05</v>
+        <v>136.37</v>
       </c>
       <c r="H25">
-        <v>240.52</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="26">
@@ -1137,13 +1137,13 @@
         <v>30.00872086031947</v>
       </c>
       <c r="F26">
-        <v>304.46</v>
+        <v>218.83</v>
       </c>
       <c r="G26">
-        <v>269.6</v>
+        <v>138.96</v>
       </c>
       <c r="H26">
-        <v>198.04</v>
+        <v>103.44</v>
       </c>
     </row>
     <row r="27">
@@ -1167,13 +1167,13 @@
         <v>30.78336108228005</v>
       </c>
       <c r="F27">
-        <v>190.83</v>
+        <v>119.32</v>
       </c>
       <c r="G27">
-        <v>266.32</v>
+        <v>112.94</v>
       </c>
       <c r="H27">
-        <v>207.47</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1197,13 +1197,13 @@
         <v>31.55160408783097</v>
       </c>
       <c r="F28">
-        <v>197.58</v>
+        <v>130.4</v>
       </c>
       <c r="G28">
-        <v>297.24</v>
+        <v>78.57000000000001</v>
       </c>
       <c r="H28">
-        <v>320.91</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="29">
@@ -1227,13 +1227,13 @@
         <v>32.3192908136941</v>
       </c>
       <c r="F29">
-        <v>267.07</v>
+        <v>180.65</v>
       </c>
       <c r="G29">
-        <v>258.51</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="H29">
-        <v>216.15</v>
+        <v>118.16</v>
       </c>
     </row>
     <row r="30">
@@ -1257,13 +1257,13 @@
         <v>33.0848575881102</v>
       </c>
       <c r="F30">
-        <v>280.43</v>
+        <v>193.11</v>
       </c>
       <c r="G30">
-        <v>304.12</v>
+        <v>163.45</v>
       </c>
       <c r="H30">
-        <v>249.11</v>
+        <v>103.28</v>
       </c>
     </row>
     <row r="31">
@@ -1287,13 +1287,13 @@
         <v>33.84831686510215</v>
       </c>
       <c r="F31">
-        <v>235.42</v>
+        <v>129.85</v>
       </c>
       <c r="G31">
-        <v>291.6</v>
+        <v>107.81</v>
       </c>
       <c r="H31">
-        <v>223.42</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32">
@@ -1317,13 +1317,13 @@
         <v>34.61141635921144</v>
       </c>
       <c r="F32">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G32">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H32">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="33">
@@ -1347,13 +1347,13 @@
         <v>35.37203335143042</v>
       </c>
       <c r="F33">
-        <v>234.86</v>
+        <v>149.59</v>
       </c>
       <c r="G33">
-        <v>299.05</v>
+        <v>136.37</v>
       </c>
       <c r="H33">
-        <v>240.52</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="34">
@@ -1377,13 +1377,13 @@
         <v>36.13089847776693</v>
       </c>
       <c r="F34">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G34">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H34">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1407,13 +1407,13 @@
         <v>36.87159318474909</v>
       </c>
       <c r="F35">
-        <v>172.92</v>
+        <v>130.11</v>
       </c>
       <c r="G35">
-        <v>237.57</v>
+        <v>58.73</v>
       </c>
       <c r="H35">
-        <v>264.33</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="36">
@@ -1437,13 +1437,13 @@
         <v>37.56199301229686</v>
       </c>
       <c r="F36">
-        <v>232.88</v>
+        <v>169.13</v>
       </c>
       <c r="G36">
-        <v>226.37</v>
+        <v>98.88</v>
       </c>
       <c r="H36">
-        <v>215.68</v>
+        <v>53.07</v>
       </c>
     </row>
     <row r="37">
@@ -1467,13 +1467,13 @@
         <v>38.24627237949855</v>
       </c>
       <c r="F37">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G37">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H37">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="38">
@@ -1497,13 +1497,13 @@
         <v>38.92863936230089</v>
       </c>
       <c r="F38">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G38">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H38">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="39">
@@ -1527,13 +1527,13 @@
         <v>39.61002524485785</v>
       </c>
       <c r="F39">
-        <v>239.71</v>
+        <v>152.73</v>
       </c>
       <c r="G39">
-        <v>322.66</v>
+        <v>115.24</v>
       </c>
       <c r="H39">
-        <v>299.66</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="40">
@@ -1557,13 +1557,13 @@
         <v>40.28254247935739</v>
       </c>
       <c r="F40">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G40">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H40">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1587,13 +1587,13 @@
         <v>40.94020898348522</v>
       </c>
       <c r="F41">
-        <v>203.77</v>
+        <v>147.37</v>
       </c>
       <c r="G41">
-        <v>252.82</v>
+        <v>87.11</v>
       </c>
       <c r="H41">
-        <v>236.07</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="42">
@@ -1617,13 +1617,13 @@
         <v>41.59118352599568</v>
       </c>
       <c r="F42">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G42">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H42">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="43">
@@ -1647,13 +1647,13 @@
         <v>42.241574113212</v>
       </c>
       <c r="F43">
-        <v>189.55</v>
+        <v>122.68</v>
       </c>
       <c r="G43">
-        <v>260.92</v>
+        <v>75.19</v>
       </c>
       <c r="H43">
-        <v>231</v>
+        <v>93.14999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -1677,13 +1677,13 @@
         <v>42.88505271774039</v>
       </c>
       <c r="F44">
-        <v>264.46</v>
+        <v>186.62</v>
       </c>
       <c r="G44">
-        <v>241.03</v>
+        <v>111.29</v>
       </c>
       <c r="H44">
-        <v>181.51</v>
+        <v>99.73999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1707,13 +1707,13 @@
         <v>43.52685002918255</v>
       </c>
       <c r="F45">
-        <v>239.71</v>
+        <v>152.73</v>
       </c>
       <c r="G45">
-        <v>322.66</v>
+        <v>115.24</v>
       </c>
       <c r="H45">
-        <v>299.66</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="46">
@@ -1737,13 +1737,13 @@
         <v>44.16086496011683</v>
       </c>
       <c r="F46">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G46">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H46">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1767,13 +1767,13 @@
         <v>44.78356610317195</v>
       </c>
       <c r="F47">
-        <v>295.86</v>
+        <v>217.26</v>
       </c>
       <c r="G47">
-        <v>270.1</v>
+        <v>162.46</v>
       </c>
       <c r="H47">
-        <v>194.81</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1797,13 +1797,13 @@
         <v>45.40377644165486</v>
       </c>
       <c r="F48">
-        <v>203.25</v>
+        <v>150.62</v>
       </c>
       <c r="G48">
-        <v>158.67</v>
+        <v>63.77</v>
       </c>
       <c r="H48">
-        <v>189.11</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="49">
@@ -1827,13 +1827,13 @@
         <v>46.02141848386773</v>
       </c>
       <c r="F49">
-        <v>181.09</v>
+        <v>130.13</v>
       </c>
       <c r="G49">
-        <v>207.07</v>
+        <v>58.12</v>
       </c>
       <c r="H49">
-        <v>224.76</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="50">
@@ -1857,13 +1857,13 @@
         <v>46.61796617891455</v>
       </c>
       <c r="F50">
-        <v>197.81</v>
+        <v>137.61</v>
       </c>
       <c r="G50">
-        <v>173.71</v>
+        <v>52.05</v>
       </c>
       <c r="H50">
-        <v>187.86</v>
+        <v>72.45999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -1887,13 +1887,13 @@
         <v>47.21235517666544</v>
       </c>
       <c r="F51">
-        <v>259.4</v>
+        <v>154.63</v>
       </c>
       <c r="G51">
-        <v>287.6</v>
+        <v>160.89</v>
       </c>
       <c r="H51">
-        <v>183.21</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="52">
@@ -1917,13 +1917,13 @@
         <v>47.79514809535232</v>
       </c>
       <c r="F52">
-        <v>188.1</v>
+        <v>124.25</v>
       </c>
       <c r="G52">
-        <v>274.87</v>
+        <v>104.93</v>
       </c>
       <c r="H52">
-        <v>234.11</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="53">
@@ -1947,13 +1947,13 @@
         <v>48.37168771078261</v>
       </c>
       <c r="F53">
-        <v>175.84</v>
+        <v>129.29</v>
       </c>
       <c r="G53">
-        <v>265.48</v>
+        <v>66.03999999999999</v>
       </c>
       <c r="H53">
-        <v>278.93</v>
+        <v>64.32000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -1977,13 +1977,13 @@
         <v>48.94506262062586</v>
       </c>
       <c r="F54">
-        <v>239.71</v>
+        <v>152.73</v>
       </c>
       <c r="G54">
-        <v>322.66</v>
+        <v>115.24</v>
       </c>
       <c r="H54">
-        <v>299.66</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="55">
@@ -2007,13 +2007,13 @@
         <v>49.51297574955436</v>
       </c>
       <c r="F55">
-        <v>235.42</v>
+        <v>129.85</v>
       </c>
       <c r="G55">
-        <v>291.6</v>
+        <v>107.81</v>
       </c>
       <c r="H55">
-        <v>223.42</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56">
@@ -2037,13 +2037,13 @@
         <v>50.07539942196176</v>
       </c>
       <c r="F56">
-        <v>190.99</v>
+        <v>145.04</v>
       </c>
       <c r="G56">
-        <v>159.1</v>
+        <v>47.63</v>
       </c>
       <c r="H56">
-        <v>219.3</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="57">
@@ -2067,13 +2067,13 @@
         <v>50.63757401391192</v>
       </c>
       <c r="F57">
-        <v>190.39</v>
+        <v>134.68</v>
       </c>
       <c r="G57">
-        <v>178.52</v>
+        <v>55</v>
       </c>
       <c r="H57">
-        <v>207.12</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="58">
@@ -2097,13 +2097,13 @@
         <v>51.19438645713023</v>
       </c>
       <c r="F58">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G58">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H58">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2127,13 +2127,13 @@
         <v>51.73644088325813</v>
       </c>
       <c r="F59">
-        <v>259.4</v>
+        <v>154.63</v>
       </c>
       <c r="G59">
-        <v>287.6</v>
+        <v>160.89</v>
       </c>
       <c r="H59">
-        <v>183.21</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="60">
@@ -2157,13 +2157,13 @@
         <v>52.27519914466878</v>
       </c>
       <c r="F60">
-        <v>236.36</v>
+        <v>156.53</v>
       </c>
       <c r="G60">
-        <v>315.85</v>
+        <v>108.62</v>
       </c>
       <c r="H60">
-        <v>299.02</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="61">
@@ -2187,13 +2187,13 @@
         <v>52.81109298082139</v>
       </c>
       <c r="F61">
-        <v>222.38</v>
+        <v>161.39</v>
       </c>
       <c r="G61">
-        <v>213.26</v>
+        <v>55.33</v>
       </c>
       <c r="H61">
-        <v>200.57</v>
+        <v>98.26000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2217,13 +2217,13 @@
         <v>53.34245355265254</v>
       </c>
       <c r="F62">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G62">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H62">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2247,13 +2247,13 @@
         <v>53.86442932636771</v>
       </c>
       <c r="F63">
-        <v>228.98</v>
+        <v>168.32</v>
       </c>
       <c r="G63">
-        <v>291.58</v>
+        <v>115.17</v>
       </c>
       <c r="H63">
-        <v>236.66</v>
+        <v>66.23</v>
       </c>
     </row>
     <row r="64">
@@ -2277,13 +2277,13 @@
         <v>54.382540201655</v>
       </c>
       <c r="F64">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G64">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H64">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="65">
@@ -2307,13 +2307,13 @@
         <v>54.8974614633095</v>
       </c>
       <c r="F65">
-        <v>197.49</v>
+        <v>133.29</v>
       </c>
       <c r="G65">
-        <v>301</v>
+        <v>87.73</v>
       </c>
       <c r="H65">
-        <v>302.77</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="66">
@@ -2337,13 +2337,13 @@
         <v>55.40624981059506</v>
       </c>
       <c r="F66">
-        <v>226.56</v>
+        <v>152.02</v>
       </c>
       <c r="G66">
-        <v>254.86</v>
+        <v>75.02</v>
       </c>
       <c r="H66">
-        <v>225.67</v>
+        <v>112.38</v>
       </c>
     </row>
     <row r="67">
@@ -2367,13 +2367,13 @@
         <v>55.91463962914909</v>
       </c>
       <c r="F67">
-        <v>266.59</v>
+        <v>170.21</v>
       </c>
       <c r="G67">
-        <v>275.9</v>
+        <v>150.65</v>
       </c>
       <c r="H67">
-        <v>184.4</v>
+        <v>80.89</v>
       </c>
     </row>
     <row r="68">
@@ -2397,13 +2397,13 @@
         <v>56.42133016547272</v>
       </c>
       <c r="F68">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G68">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H68">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -2427,13 +2427,13 @@
         <v>56.90382115159692</v>
       </c>
       <c r="F69">
-        <v>239.71</v>
+        <v>152.73</v>
       </c>
       <c r="G69">
-        <v>322.66</v>
+        <v>115.24</v>
       </c>
       <c r="H69">
-        <v>299.66</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="70">
@@ -2457,13 +2457,13 @@
         <v>57.38413129994011</v>
       </c>
       <c r="F70">
-        <v>214.5</v>
+        <v>158.02</v>
       </c>
       <c r="G70">
-        <v>206.18</v>
+        <v>49.15</v>
       </c>
       <c r="H70">
-        <v>196.04</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="71">
@@ -2487,13 +2487,13 @@
         <v>57.85522547136609</v>
       </c>
       <c r="F71">
-        <v>172.92</v>
+        <v>130.11</v>
       </c>
       <c r="G71">
-        <v>237.57</v>
+        <v>58.73</v>
       </c>
       <c r="H71">
-        <v>264.33</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="72">
@@ -2517,13 +2517,13 @@
         <v>58.32304285099927</v>
       </c>
       <c r="F72">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G72">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H72">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="73">
@@ -2547,13 +2547,13 @@
         <v>58.78766093053747</v>
       </c>
       <c r="F73">
-        <v>181.09</v>
+        <v>130.13</v>
       </c>
       <c r="G73">
-        <v>207.07</v>
+        <v>58.12</v>
       </c>
       <c r="H73">
-        <v>224.76</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="74">
@@ -2577,13 +2577,13 @@
         <v>59.24253581285732</v>
       </c>
       <c r="F74">
-        <v>184.51</v>
+        <v>132.9</v>
       </c>
       <c r="G74">
-        <v>183.28</v>
+        <v>52.31</v>
       </c>
       <c r="H74">
-        <v>201.3</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="75">
@@ -2607,13 +2607,13 @@
         <v>59.69291894426529</v>
       </c>
       <c r="F75">
-        <v>234.86</v>
+        <v>149.59</v>
       </c>
       <c r="G75">
-        <v>299.05</v>
+        <v>136.37</v>
       </c>
       <c r="H75">
-        <v>240.52</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="76">
@@ -2637,13 +2637,13 @@
         <v>60.11951074066759</v>
       </c>
       <c r="F76">
-        <v>181.53</v>
+        <v>135.49</v>
       </c>
       <c r="G76">
-        <v>206.63</v>
+        <v>37.99</v>
       </c>
       <c r="H76">
-        <v>208.06</v>
+        <v>72.79000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -2667,13 +2667,13 @@
         <v>60.53659458250559</v>
       </c>
       <c r="F77">
-        <v>259.4</v>
+        <v>154.63</v>
       </c>
       <c r="G77">
-        <v>287.6</v>
+        <v>160.89</v>
       </c>
       <c r="H77">
-        <v>183.21</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="78">
@@ -2697,13 +2697,13 @@
         <v>60.95349161400069</v>
       </c>
       <c r="F78">
-        <v>236.36</v>
+        <v>156.53</v>
       </c>
       <c r="G78">
-        <v>315.85</v>
+        <v>108.62</v>
       </c>
       <c r="H78">
-        <v>299.02</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="79">
@@ -2727,13 +2727,13 @@
         <v>61.3615241487793</v>
       </c>
       <c r="F79">
-        <v>236.36</v>
+        <v>156.53</v>
       </c>
       <c r="G79">
-        <v>315.85</v>
+        <v>108.62</v>
       </c>
       <c r="H79">
-        <v>299.02</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="80">
@@ -2757,13 +2757,13 @@
         <v>61.76181028133831</v>
       </c>
       <c r="F80">
-        <v>180.8</v>
+        <v>133.45</v>
       </c>
       <c r="G80">
-        <v>225.92</v>
+        <v>51.17</v>
       </c>
       <c r="H80">
-        <v>235.07</v>
+        <v>62.03</v>
       </c>
     </row>
     <row r="81">
@@ -2787,13 +2787,13 @@
         <v>62.1593565288679</v>
       </c>
       <c r="F81">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G81">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H81">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="82">
@@ -2817,13 +2817,13 @@
         <v>62.55336583390492</v>
       </c>
       <c r="F82">
-        <v>175.42</v>
+        <v>123.21</v>
       </c>
       <c r="G82">
-        <v>164.26</v>
+        <v>47.6</v>
       </c>
       <c r="H82">
-        <v>226.34</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="83">
@@ -2847,13 +2847,13 @@
         <v>62.94711083690121</v>
       </c>
       <c r="F83">
-        <v>254.03</v>
+        <v>168.85</v>
       </c>
       <c r="G83">
-        <v>255.53</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="H83">
-        <v>213.38</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="84">
@@ -2877,13 +2877,13 @@
         <v>63.3325836011571</v>
       </c>
       <c r="F84">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G84">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H84">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -2907,13 +2907,13 @@
         <v>63.70564108840079</v>
       </c>
       <c r="F85">
-        <v>234.86</v>
+        <v>149.59</v>
       </c>
       <c r="G85">
-        <v>299.05</v>
+        <v>136.37</v>
       </c>
       <c r="H85">
-        <v>240.52</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="86">
@@ -2937,13 +2937,13 @@
         <v>64.07437979727231</v>
       </c>
       <c r="F86">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G86">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H86">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -2967,13 +2967,13 @@
         <v>64.43812721053717</v>
       </c>
       <c r="F87">
-        <v>261.55</v>
+        <v>181.8</v>
       </c>
       <c r="G87">
-        <v>312.36</v>
+        <v>129.63</v>
       </c>
       <c r="H87">
-        <v>262.78</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="88">
@@ -2997,13 +2997,13 @@
         <v>64.80106511231605</v>
       </c>
       <c r="F88">
-        <v>160.52</v>
+        <v>113.96</v>
       </c>
       <c r="G88">
-        <v>254.62</v>
+        <v>57.24</v>
       </c>
       <c r="H88">
-        <v>251.13</v>
+        <v>66.70999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -3027,13 +3027,13 @@
         <v>65.16141949624142</v>
       </c>
       <c r="F89">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G89">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H89">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -3057,13 +3057,13 @@
         <v>65.50785305016871</v>
       </c>
       <c r="F90">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G90">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H90">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="91">
@@ -3087,13 +3087,13 @@
         <v>65.84936172994459</v>
       </c>
       <c r="F91">
-        <v>176.21</v>
+        <v>128.78</v>
       </c>
       <c r="G91">
-        <v>213.39</v>
+        <v>37.83</v>
       </c>
       <c r="H91">
-        <v>211.64</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="92">
@@ -3117,13 +3117,13 @@
         <v>66.18815266517612</v>
       </c>
       <c r="F92">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G92">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H92">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="93">
@@ -3147,13 +3147,13 @@
         <v>66.52471294653519</v>
       </c>
       <c r="F93">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G93">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H93">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -3177,13 +3177,13 @@
         <v>66.85052955750609</v>
       </c>
       <c r="F94">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G94">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H94">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="95">
@@ -3207,13 +3207,13 @@
         <v>67.17006657339434</v>
       </c>
       <c r="F95">
-        <v>261.55</v>
+        <v>181.8</v>
       </c>
       <c r="G95">
-        <v>312.36</v>
+        <v>129.63</v>
       </c>
       <c r="H95">
-        <v>262.78</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="96">
@@ -3237,13 +3237,13 @@
         <v>67.48746703247177</v>
       </c>
       <c r="F96">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G96">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H96">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="97">
@@ -3267,13 +3267,13 @@
         <v>67.80089327447618</v>
       </c>
       <c r="F97">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G97">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H97">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="98">
@@ -3297,13 +3297,13 @@
         <v>68.1129357361627</v>
       </c>
       <c r="F98">
-        <v>229.19</v>
+        <v>169.54</v>
       </c>
       <c r="G98">
-        <v>203.84</v>
+        <v>69.95</v>
       </c>
       <c r="H98">
-        <v>176.09</v>
+        <v>95.77</v>
       </c>
     </row>
     <row r="99">
@@ -3327,13 +3327,13 @@
         <v>68.42425863208391</v>
       </c>
       <c r="F99">
-        <v>188.1</v>
+        <v>124.25</v>
       </c>
       <c r="G99">
-        <v>274.87</v>
+        <v>104.93</v>
       </c>
       <c r="H99">
-        <v>234.11</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="100">
@@ -3357,13 +3357,13 @@
         <v>68.72695642528363</v>
       </c>
       <c r="F100">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G100">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H100">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="101">
@@ -3387,13 +3387,13 @@
         <v>69.02817772488416</v>
       </c>
       <c r="F101">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G101">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H101">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="102">
@@ -3417,13 +3417,13 @@
         <v>69.32183112992611</v>
       </c>
       <c r="F102">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G102">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H102">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="103">
@@ -3447,13 +3447,13 @@
         <v>69.61537244876229</v>
       </c>
       <c r="F103">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G103">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H103">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="104">
@@ -3477,13 +3477,13 @@
         <v>69.907253231217</v>
       </c>
       <c r="F104">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G104">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H104">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="105">
@@ -3507,13 +3507,13 @@
         <v>70.19904683551167</v>
       </c>
       <c r="F105">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G105">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H105">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="106">
@@ -3537,13 +3537,13 @@
         <v>70.48723292451758</v>
       </c>
       <c r="F106">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G106">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H106">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="107">
@@ -3567,13 +3567,13 @@
         <v>70.77529447329489</v>
       </c>
       <c r="F107">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G107">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H107">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="108">
@@ -3597,13 +3597,13 @@
         <v>71.05904001126065</v>
       </c>
       <c r="F108">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G108">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H108">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="109">
@@ -3627,13 +3627,13 @@
         <v>71.34233582062312</v>
       </c>
       <c r="F109">
-        <v>239.71</v>
+        <v>152.73</v>
       </c>
       <c r="G109">
-        <v>322.66</v>
+        <v>115.24</v>
       </c>
       <c r="H109">
-        <v>299.66</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="110">
@@ -3657,13 +3657,13 @@
         <v>71.6218165476491</v>
       </c>
       <c r="F110">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G110">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H110">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="111">
@@ -3687,13 +3687,13 @@
         <v>71.90100529702804</v>
       </c>
       <c r="F111">
-        <v>266.52</v>
+        <v>184.74</v>
       </c>
       <c r="G111">
-        <v>252.73</v>
+        <v>117.93</v>
       </c>
       <c r="H111">
-        <v>203.13</v>
+        <v>101.66</v>
       </c>
     </row>
     <row r="112">
@@ -3717,13 +3717,13 @@
         <v>72.18018851128569</v>
       </c>
       <c r="F112">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G112">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H112">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="113">
@@ -3747,13 +3747,13 @@
         <v>72.45312534118834</v>
       </c>
       <c r="F113">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G113">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H113">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="114">
@@ -3777,13 +3777,13 @@
         <v>72.72467839077309</v>
       </c>
       <c r="F114">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G114">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H114">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="115">
@@ -3807,13 +3807,13 @@
         <v>72.99167326799068</v>
       </c>
       <c r="F115">
-        <v>188.1</v>
+        <v>124.25</v>
       </c>
       <c r="G115">
-        <v>274.87</v>
+        <v>104.93</v>
       </c>
       <c r="H115">
-        <v>234.11</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="116">
@@ -3837,13 +3837,13 @@
         <v>73.25787385530579</v>
       </c>
       <c r="F116">
-        <v>257.83</v>
+        <v>129.26</v>
       </c>
       <c r="G116">
-        <v>312.39</v>
+        <v>142.21</v>
       </c>
       <c r="H116">
-        <v>228.61</v>
+        <v>109.71</v>
       </c>
     </row>
     <row r="117">
@@ -3867,13 +3867,13 @@
         <v>73.52227276064698</v>
       </c>
       <c r="F117">
-        <v>189.55</v>
+        <v>122.68</v>
       </c>
       <c r="G117">
-        <v>260.92</v>
+        <v>75.19</v>
       </c>
       <c r="H117">
-        <v>231</v>
+        <v>93.14999999999999</v>
       </c>
     </row>
     <row r="118">
@@ -3897,13 +3897,13 @@
         <v>73.77426607543822</v>
       </c>
       <c r="F118">
-        <v>234.86</v>
+        <v>149.59</v>
       </c>
       <c r="G118">
-        <v>299.05</v>
+        <v>136.37</v>
       </c>
       <c r="H118">
-        <v>240.52</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="119">
@@ -3927,13 +3927,13 @@
         <v>74.02575846175438</v>
       </c>
       <c r="F119">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G119">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H119">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="120">
@@ -3957,13 +3957,13 @@
         <v>74.27705573504571</v>
       </c>
       <c r="F120">
-        <v>293.21</v>
+        <v>225.6</v>
       </c>
       <c r="G120">
-        <v>280.06</v>
+        <v>145.82</v>
       </c>
       <c r="H120">
-        <v>219.3</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="121">
@@ -3987,13 +3987,13 @@
         <v>74.52580408499145</v>
       </c>
       <c r="F121">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G121">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H121">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="122">
@@ -4017,13 +4017,13 @@
         <v>74.77395879318084</v>
       </c>
       <c r="F122">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G122">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H122">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -4047,13 +4047,13 @@
         <v>75.01941097840935</v>
       </c>
       <c r="F123">
-        <v>271.67</v>
+        <v>147.56</v>
       </c>
       <c r="G123">
-        <v>308.19</v>
+        <v>170.14</v>
       </c>
       <c r="H123">
-        <v>197.49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="124">
@@ -4077,13 +4077,13 @@
         <v>75.2634517077136</v>
       </c>
       <c r="F124">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G124">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H124">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="125">
@@ -4107,13 +4107,13 @@
         <v>75.50688218989767</v>
       </c>
       <c r="F125">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G125">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H125">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="126">
@@ -4137,13 +4137,13 @@
         <v>75.74863553033644</v>
       </c>
       <c r="F126">
-        <v>234.86</v>
+        <v>149.59</v>
       </c>
       <c r="G126">
-        <v>299.05</v>
+        <v>136.37</v>
       </c>
       <c r="H126">
-        <v>240.52</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="127">
@@ -4167,13 +4167,13 @@
         <v>75.98373703878705</v>
       </c>
       <c r="F127">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G127">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H127">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -4197,13 +4197,13 @@
         <v>76.21528915072227</v>
       </c>
       <c r="F128">
-        <v>172.92</v>
+        <v>130.11</v>
       </c>
       <c r="G128">
-        <v>237.57</v>
+        <v>58.73</v>
       </c>
       <c r="H128">
-        <v>264.33</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="129">
@@ -4227,13 +4227,13 @@
         <v>76.44548377416561</v>
       </c>
       <c r="F129">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G129">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H129">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="130">
@@ -4257,13 +4257,13 @@
         <v>76.66837342131076</v>
       </c>
       <c r="F130">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G130">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H130">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -4287,13 +4287,13 @@
         <v>76.89114544712889</v>
       </c>
       <c r="F131">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G131">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H131">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="132">
@@ -4317,13 +4317,13 @@
         <v>77.1091212903652</v>
       </c>
       <c r="F132">
-        <v>239.71</v>
+        <v>152.73</v>
       </c>
       <c r="G132">
-        <v>322.66</v>
+        <v>115.24</v>
       </c>
       <c r="H132">
-        <v>299.66</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="133">
@@ -4347,13 +4347,13 @@
         <v>77.32604961190083</v>
       </c>
       <c r="F133">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G133">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H133">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="134">
@@ -4377,13 +4377,13 @@
         <v>77.53873664676209</v>
       </c>
       <c r="F134">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G134">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H134">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="135">
@@ -4407,13 +4407,13 @@
         <v>77.75081481828349</v>
       </c>
       <c r="F135">
-        <v>293.58</v>
+        <v>150.62</v>
       </c>
       <c r="G135">
-        <v>316.07</v>
+        <v>151.76</v>
       </c>
       <c r="H135">
-        <v>223.42</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="136">
@@ -4437,13 +4437,13 @@
         <v>77.96257472033177</v>
       </c>
       <c r="F136">
-        <v>235.42</v>
+        <v>129.85</v>
       </c>
       <c r="G136">
-        <v>291.6</v>
+        <v>107.81</v>
       </c>
       <c r="H136">
-        <v>223.42</v>
+        <v>116</v>
       </c>
     </row>
     <row r="137">
@@ -4467,13 +4467,13 @@
         <v>78.17429034140989</v>
       </c>
       <c r="F137">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G137">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H137">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="138">
@@ -4497,13 +4497,13 @@
         <v>78.38485880860445</v>
       </c>
       <c r="F138">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G138">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H138">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="139">
@@ -4527,13 +4527,13 @@
         <v>78.59282715258168</v>
       </c>
       <c r="F139">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G139">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H139">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="140">
@@ -4557,13 +4557,13 @@
         <v>78.79914879798061</v>
       </c>
       <c r="F140">
-        <v>304.46</v>
+        <v>218.83</v>
       </c>
       <c r="G140">
-        <v>269.6</v>
+        <v>138.96</v>
       </c>
       <c r="H140">
-        <v>198.04</v>
+        <v>103.44</v>
       </c>
     </row>
     <row r="141">
@@ -4587,13 +4587,13 @@
         <v>79.00493076905558</v>
       </c>
       <c r="F141">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G141">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H141">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="142">
@@ -4617,13 +4617,13 @@
         <v>79.21067122672098</v>
       </c>
       <c r="F142">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G142">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H142">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="143">
@@ -4647,13 +4647,13 @@
         <v>79.41632035488541</v>
       </c>
       <c r="F143">
-        <v>256.98</v>
+        <v>186.61</v>
       </c>
       <c r="G143">
-        <v>228.25</v>
+        <v>86.69</v>
       </c>
       <c r="H143">
-        <v>190.71</v>
+        <v>102.48</v>
       </c>
     </row>
     <row r="144">
@@ -4677,13 +4677,13 @@
         <v>79.61815440071339</v>
       </c>
       <c r="F144">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G144">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H144">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="145">
@@ -4707,13 +4707,13 @@
         <v>79.81620657493255</v>
       </c>
       <c r="F145">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G145">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H145">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="146">
@@ -4737,13 +4737,13 @@
         <v>80.01407193880881</v>
       </c>
       <c r="F146">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G146">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H146">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="147">
@@ -4767,13 +4767,13 @@
         <v>80.21181414623675</v>
       </c>
       <c r="F147">
-        <v>270.89</v>
+        <v>133.65</v>
       </c>
       <c r="G147">
-        <v>321.03</v>
+        <v>160.34</v>
       </c>
       <c r="H147">
-        <v>229.65</v>
+        <v>104.81</v>
       </c>
     </row>
     <row r="148">
@@ -4797,13 +4797,13 @@
         <v>80.40938476490528</v>
       </c>
       <c r="F148">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G148">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H148">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="149">
@@ -4827,13 +4827,13 @@
         <v>80.60507897746272</v>
       </c>
       <c r="F149">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G149">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H149">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="150">
@@ -4857,13 +4857,13 @@
         <v>80.79610708278823</v>
       </c>
       <c r="F150">
-        <v>236.36</v>
+        <v>156.53</v>
       </c>
       <c r="G150">
-        <v>315.85</v>
+        <v>108.62</v>
       </c>
       <c r="H150">
-        <v>299.02</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="151">
@@ -4887,13 +4887,13 @@
         <v>80.98306272263814</v>
       </c>
       <c r="F151">
-        <v>261.55</v>
+        <v>181.8</v>
       </c>
       <c r="G151">
-        <v>312.36</v>
+        <v>129.63</v>
       </c>
       <c r="H151">
-        <v>262.78</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="152">
@@ -4917,13 +4917,13 @@
         <v>81.16550447109107</v>
       </c>
       <c r="F152">
-        <v>266.52</v>
+        <v>184.74</v>
       </c>
       <c r="G152">
-        <v>252.73</v>
+        <v>117.93</v>
       </c>
       <c r="H152">
-        <v>203.13</v>
+        <v>101.66</v>
       </c>
     </row>
     <row r="153">
@@ -4947,13 +4947,13 @@
         <v>81.34774833895854</v>
       </c>
       <c r="F153">
-        <v>270.89</v>
+        <v>133.65</v>
       </c>
       <c r="G153">
-        <v>321.03</v>
+        <v>160.34</v>
       </c>
       <c r="H153">
-        <v>229.65</v>
+        <v>104.81</v>
       </c>
     </row>
     <row r="154">
@@ -4977,13 +4977,13 @@
         <v>81.52906645779335</v>
       </c>
       <c r="F154">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G154">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H154">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="155">
@@ -5007,13 +5007,13 @@
         <v>81.71015625287566</v>
       </c>
       <c r="F155">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G155">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H155">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="156">
@@ -5037,13 +5037,13 @@
         <v>81.89055139023843</v>
       </c>
       <c r="F156">
-        <v>228.98</v>
+        <v>168.32</v>
       </c>
       <c r="G156">
-        <v>291.58</v>
+        <v>115.17</v>
       </c>
       <c r="H156">
-        <v>236.66</v>
+        <v>66.23</v>
       </c>
     </row>
     <row r="157">
@@ -5067,13 +5067,13 @@
         <v>82.07032797779908</v>
       </c>
       <c r="F157">
-        <v>234.86</v>
+        <v>149.59</v>
       </c>
       <c r="G157">
-        <v>299.05</v>
+        <v>136.37</v>
       </c>
       <c r="H157">
-        <v>240.52</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="158">
@@ -5097,13 +5097,13 @@
         <v>82.24864467712433</v>
       </c>
       <c r="F158">
-        <v>188.1</v>
+        <v>124.25</v>
       </c>
       <c r="G158">
-        <v>274.87</v>
+        <v>104.93</v>
       </c>
       <c r="H158">
-        <v>234.11</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="159">
@@ -5127,13 +5127,13 @@
         <v>82.42694061974484</v>
       </c>
       <c r="F159">
-        <v>203.77</v>
+        <v>147.37</v>
       </c>
       <c r="G159">
-        <v>252.82</v>
+        <v>87.11</v>
       </c>
       <c r="H159">
-        <v>236.07</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="160">
@@ -5157,13 +5157,13 @@
         <v>82.60492106045287</v>
       </c>
       <c r="F160">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G160">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H160">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="161">
@@ -5187,13 +5187,13 @@
         <v>82.77756702803536</v>
       </c>
       <c r="F161">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G161">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H161">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="162">
@@ -5217,13 +5217,13 @@
         <v>82.95012720123816</v>
       </c>
       <c r="F162">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G162">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H162">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="163">
@@ -5247,13 +5247,13 @@
         <v>83.12020764011129</v>
       </c>
       <c r="F163">
-        <v>256.98</v>
+        <v>186.61</v>
       </c>
       <c r="G163">
-        <v>228.25</v>
+        <v>86.69</v>
       </c>
       <c r="H163">
-        <v>190.71</v>
+        <v>102.48</v>
       </c>
     </row>
     <row r="164">
@@ -5277,13 +5277,13 @@
         <v>83.29020505216533</v>
       </c>
       <c r="F164">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G164">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H164">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="165">
@@ -5307,13 +5307,13 @@
         <v>83.46019139397684</v>
       </c>
       <c r="F165">
-        <v>271.67</v>
+        <v>147.56</v>
       </c>
       <c r="G165">
-        <v>308.19</v>
+        <v>170.14</v>
       </c>
       <c r="H165">
-        <v>197.49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="166">
@@ -5337,13 +5337,13 @@
         <v>83.62814634628168</v>
       </c>
       <c r="F166">
-        <v>235.42</v>
+        <v>129.85</v>
       </c>
       <c r="G166">
-        <v>291.6</v>
+        <v>107.81</v>
       </c>
       <c r="H166">
-        <v>223.42</v>
+        <v>116</v>
       </c>
     </row>
     <row r="167">
@@ -5367,13 +5367,13 @@
         <v>83.79596845567599</v>
       </c>
       <c r="F167">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G167">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H167">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="168">
@@ -5397,13 +5397,13 @@
         <v>83.9637518192214</v>
       </c>
       <c r="F168">
-        <v>271.67</v>
+        <v>147.56</v>
       </c>
       <c r="G168">
-        <v>308.19</v>
+        <v>170.14</v>
       </c>
       <c r="H168">
-        <v>197.49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="169">
@@ -5427,13 +5427,13 @@
         <v>84.130561001423</v>
       </c>
       <c r="F169">
-        <v>300.53</v>
+        <v>212.24</v>
       </c>
       <c r="G169">
-        <v>261.6</v>
+        <v>130.98</v>
       </c>
       <c r="H169">
-        <v>194.14</v>
+        <v>90.41</v>
       </c>
     </row>
     <row r="170">
@@ -5457,13 +5457,13 @@
         <v>84.29608880305022</v>
       </c>
       <c r="F170">
-        <v>304.46</v>
+        <v>218.83</v>
       </c>
       <c r="G170">
-        <v>269.6</v>
+        <v>138.96</v>
       </c>
       <c r="H170">
-        <v>198.04</v>
+        <v>103.44</v>
       </c>
     </row>
     <row r="171">
@@ -5487,13 +5487,13 @@
         <v>84.46012212193413</v>
       </c>
       <c r="F171">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G171">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H171">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -5517,13 +5517,13 @@
         <v>84.6241139274085</v>
       </c>
       <c r="F172">
-        <v>270.89</v>
+        <v>133.65</v>
       </c>
       <c r="G172">
-        <v>321.03</v>
+        <v>160.34</v>
       </c>
       <c r="H172">
-        <v>229.65</v>
+        <v>104.81</v>
       </c>
     </row>
     <row r="173">
@@ -5547,13 +5547,13 @@
         <v>84.78638984528865</v>
       </c>
       <c r="F173">
-        <v>378.85</v>
+        <v>173.21</v>
       </c>
       <c r="G173">
-        <v>388.17</v>
+        <v>189.41</v>
       </c>
       <c r="H173">
-        <v>271.93</v>
+        <v>161.08</v>
       </c>
     </row>
     <row r="174">
@@ -5577,13 +5577,13 @@
         <v>84.94729582065411</v>
       </c>
       <c r="F174">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G174">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H174">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="175">
@@ -5607,13 +5607,13 @@
         <v>85.10722207955448</v>
       </c>
       <c r="F175">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G175">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H175">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="176">
@@ -5637,13 +5637,13 @@
         <v>85.26679962581474</v>
       </c>
       <c r="F176">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G176">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H176">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="177">
@@ -5667,13 +5667,13 @@
         <v>85.42602292431361</v>
       </c>
       <c r="F177">
-        <v>234.86</v>
+        <v>149.59</v>
       </c>
       <c r="G177">
-        <v>299.05</v>
+        <v>136.37</v>
       </c>
       <c r="H177">
-        <v>240.52</v>
+        <v>99.12</v>
       </c>
     </row>
     <row r="178">
@@ -5697,13 +5697,13 @@
         <v>85.58468717556407</v>
       </c>
       <c r="F178">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G178">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H178">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="179">
@@ -5727,13 +5727,13 @@
         <v>85.74193997089026</v>
       </c>
       <c r="F179">
-        <v>297.18</v>
+        <v>142.39</v>
       </c>
       <c r="G179">
-        <v>339.25</v>
+        <v>155.15</v>
       </c>
       <c r="H179">
-        <v>247.15</v>
+        <v>130.83</v>
       </c>
     </row>
     <row r="180">
@@ -5757,13 +5757,13 @@
         <v>85.89886065894015</v>
       </c>
       <c r="F180">
-        <v>259.4</v>
+        <v>154.63</v>
       </c>
       <c r="G180">
-        <v>287.6</v>
+        <v>160.89</v>
       </c>
       <c r="H180">
-        <v>183.21</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="181">
@@ -5787,13 +5787,13 @@
         <v>86.05561806091252</v>
       </c>
       <c r="F181">
-        <v>239.71</v>
+        <v>152.73</v>
       </c>
       <c r="G181">
-        <v>322.66</v>
+        <v>115.24</v>
       </c>
       <c r="H181">
-        <v>299.66</v>
+        <v>108.32</v>
       </c>
     </row>
     <row r="182">
@@ -5817,13 +5817,13 @@
         <v>86.21235193861949</v>
       </c>
       <c r="F182">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G182">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H182">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -5847,13 +5847,13 @@
         <v>86.36885749257401</v>
       </c>
       <c r="F183">
-        <v>378.85</v>
+        <v>173.21</v>
       </c>
       <c r="G183">
-        <v>388.17</v>
+        <v>189.41</v>
       </c>
       <c r="H183">
-        <v>271.93</v>
+        <v>161.08</v>
       </c>
     </row>
     <row r="184">
@@ -5877,13 +5877,13 @@
         <v>86.52472789136263</v>
       </c>
       <c r="F184">
-        <v>257.83</v>
+        <v>129.26</v>
       </c>
       <c r="G184">
-        <v>312.39</v>
+        <v>142.21</v>
       </c>
       <c r="H184">
-        <v>228.61</v>
+        <v>109.71</v>
       </c>
     </row>
     <row r="185">
@@ -5907,13 +5907,13 @@
         <v>86.67999772949327</v>
       </c>
       <c r="F185">
-        <v>344.27</v>
+        <v>166.29</v>
       </c>
       <c r="G185">
-        <v>340</v>
+        <v>154.57</v>
       </c>
       <c r="H185">
-        <v>254.3</v>
+        <v>147.5</v>
       </c>
     </row>
     <row r="186">
@@ -5937,13 +5937,13 @@
         <v>86.8349908115603</v>
       </c>
       <c r="F186">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G186">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H186">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -5967,13 +5967,13 @@
         <v>86.98643172955131</v>
       </c>
       <c r="F187">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G187">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H187">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="188">
@@ -5997,13 +5997,13 @@
         <v>87.13720843298974</v>
       </c>
       <c r="F188">
-        <v>176.21</v>
+        <v>128.78</v>
       </c>
       <c r="G188">
-        <v>213.39</v>
+        <v>37.83</v>
       </c>
       <c r="H188">
-        <v>211.64</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="189">
@@ -6027,13 +6027,13 @@
         <v>87.28792425009416</v>
       </c>
       <c r="F189">
-        <v>236.36</v>
+        <v>156.53</v>
       </c>
       <c r="G189">
-        <v>315.85</v>
+        <v>108.62</v>
       </c>
       <c r="H189">
-        <v>299.02</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="190">
@@ -6057,13 +6057,13 @@
         <v>87.43748322685283</v>
       </c>
       <c r="F190">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G190">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H190">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="191">
@@ -6087,13 +6087,13 @@
         <v>87.58492501972511</v>
       </c>
       <c r="F191">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G191">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H191">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="192">
@@ -6117,13 +6117,13 @@
         <v>87.729740397554</v>
       </c>
       <c r="F192">
-        <v>188.1</v>
+        <v>124.25</v>
       </c>
       <c r="G192">
-        <v>274.87</v>
+        <v>104.93</v>
       </c>
       <c r="H192">
-        <v>234.11</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="193">
@@ -6147,13 +6147,13 @@
         <v>87.87153083160797</v>
       </c>
       <c r="F193">
-        <v>178.67</v>
+        <v>116.13</v>
       </c>
       <c r="G193">
-        <v>264.7</v>
+        <v>85</v>
       </c>
       <c r="H193">
-        <v>233.92</v>
+        <v>79.73999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -6177,13 +6177,13 @@
         <v>88.01282172096718</v>
       </c>
       <c r="F194">
-        <v>190.83</v>
+        <v>119.32</v>
       </c>
       <c r="G194">
-        <v>266.32</v>
+        <v>112.94</v>
       </c>
       <c r="H194">
-        <v>207.47</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -6207,13 +6207,13 @@
         <v>88.15335845005313</v>
       </c>
       <c r="F195">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G195">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H195">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="196">
@@ -6237,13 +6237,13 @@
         <v>88.29164515234218</v>
       </c>
       <c r="F196">
-        <v>201.41</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="G196">
-        <v>257.33</v>
+        <v>119.91</v>
       </c>
       <c r="H196">
-        <v>202.76</v>
+        <v>101.93</v>
       </c>
     </row>
     <row r="197">
@@ -6267,13 +6267,13 @@
         <v>88.42677130038514</v>
       </c>
       <c r="F197">
-        <v>203.77</v>
+        <v>147.37</v>
       </c>
       <c r="G197">
-        <v>252.82</v>
+        <v>87.11</v>
       </c>
       <c r="H197">
-        <v>236.07</v>
+        <v>62.95</v>
       </c>
     </row>
     <row r="198">
@@ -6297,13 +6297,13 @@
         <v>88.56170095162297</v>
       </c>
       <c r="F198">
-        <v>169</v>
+        <v>126.02</v>
       </c>
       <c r="G198">
-        <v>233.76</v>
+        <v>49.33</v>
       </c>
       <c r="H198">
-        <v>241.4</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="199">
@@ -6327,13 +6327,13 @@
         <v>88.69379938833036</v>
       </c>
       <c r="F199">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G199">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H199">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="200">
@@ -6357,13 +6357,13 @@
         <v>88.82579680907455</v>
       </c>
       <c r="F200">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G200">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H200">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="201">
@@ -6387,13 +6387,13 @@
         <v>88.95745381986053</v>
       </c>
       <c r="F201">
-        <v>188.1</v>
+        <v>124.25</v>
       </c>
       <c r="G201">
-        <v>274.87</v>
+        <v>104.93</v>
       </c>
       <c r="H201">
-        <v>234.11</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="202">
@@ -6417,13 +6417,13 @@
         <v>89.0888852744547</v>
       </c>
       <c r="F202">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G202">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H202">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="203">
@@ -6447,13 +6447,13 @@
         <v>89.21780516777189</v>
       </c>
       <c r="F203">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G203">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H203">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="204">
@@ -6477,13 +6477,13 @@
         <v>89.34658529927695</v>
       </c>
       <c r="F204">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G204">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H204">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -6507,13 +6507,13 @@
         <v>89.47414770410228</v>
       </c>
       <c r="F205">
-        <v>172.92</v>
+        <v>130.11</v>
       </c>
       <c r="G205">
-        <v>237.57</v>
+        <v>58.73</v>
       </c>
       <c r="H205">
-        <v>264.33</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="206">
@@ -6537,13 +6537,13 @@
         <v>89.5998170974527</v>
       </c>
       <c r="F206">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G206">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H206">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="207">
@@ -6567,13 +6567,13 @@
         <v>89.7247724601591</v>
       </c>
       <c r="F207">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G207">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H207">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="208">
@@ -6597,13 +6597,13 @@
         <v>89.84947874240828</v>
       </c>
       <c r="F208">
-        <v>254.03</v>
+        <v>168.85</v>
       </c>
       <c r="G208">
-        <v>255.53</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="H208">
-        <v>213.38</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="209">
@@ -6627,13 +6627,13 @@
         <v>89.97385291738115</v>
       </c>
       <c r="F209">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G209">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H209">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="210">
@@ -6657,13 +6657,13 @@
         <v>90.09794203360855</v>
       </c>
       <c r="F210">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G210">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H210">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="211">
@@ -6687,13 +6687,13 @@
         <v>90.22172395060535</v>
       </c>
       <c r="F211">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G211">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H211">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="212">
@@ -6717,13 +6717,13 @@
         <v>90.3454837271171</v>
       </c>
       <c r="F212">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G212">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H212">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="213">
@@ -6747,13 +6747,13 @@
         <v>90.46923520094691</v>
       </c>
       <c r="F213">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G213">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H213">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="214">
@@ -6777,13 +6777,13 @@
         <v>90.59270715115252</v>
       </c>
       <c r="F214">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G214">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H214">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="215">
@@ -6807,13 +6807,13 @@
         <v>90.71572522141385</v>
       </c>
       <c r="F215">
-        <v>270.89</v>
+        <v>133.65</v>
       </c>
       <c r="G215">
-        <v>321.03</v>
+        <v>160.34</v>
       </c>
       <c r="H215">
-        <v>229.65</v>
+        <v>104.81</v>
       </c>
     </row>
     <row r="216">
@@ -6837,13 +6837,13 @@
         <v>90.83613763333658</v>
       </c>
       <c r="F216">
-        <v>264.89</v>
+        <v>176.41</v>
       </c>
       <c r="G216">
-        <v>277.86</v>
+        <v>160.61</v>
       </c>
       <c r="H216">
-        <v>192.92</v>
+        <v>82.16</v>
       </c>
     </row>
     <row r="217">
@@ -6867,13 +6867,13 @@
         <v>90.95602005739755</v>
       </c>
       <c r="F217">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G217">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H217">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="218">
@@ -6897,13 +6897,13 @@
         <v>91.07508743485127</v>
       </c>
       <c r="F218">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G218">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H218">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="219">
@@ -6927,13 +6927,13 @@
         <v>91.1921441795031</v>
       </c>
       <c r="F219">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G219">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H219">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="220">
@@ -6957,13 +6957,13 @@
         <v>91.3086584822703</v>
       </c>
       <c r="F220">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G220">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H220">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="221">
@@ -6987,13 +6987,13 @@
         <v>91.42331575185089</v>
       </c>
       <c r="F221">
-        <v>258.16</v>
+        <v>158.85</v>
       </c>
       <c r="G221">
-        <v>286.31</v>
+        <v>164.68</v>
       </c>
       <c r="H221">
-        <v>175.79</v>
+        <v>69.12</v>
       </c>
     </row>
     <row r="222">
@@ -7017,13 +7017,13 @@
         <v>91.53750253612338</v>
       </c>
       <c r="F222">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G222">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H222">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="223">
@@ -7047,13 +7047,13 @@
         <v>91.65065010137712</v>
       </c>
       <c r="F223">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G223">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H223">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="224">
@@ -7077,13 +7077,13 @@
         <v>91.76326906254944</v>
       </c>
       <c r="F224">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G224">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H224">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="225">
@@ -7107,13 +7107,13 @@
         <v>91.87572612142458</v>
       </c>
       <c r="F225">
-        <v>190.83</v>
+        <v>119.32</v>
       </c>
       <c r="G225">
-        <v>266.32</v>
+        <v>112.94</v>
       </c>
       <c r="H225">
-        <v>207.47</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="226">
@@ -7137,13 +7137,13 @@
         <v>91.98789258643293</v>
       </c>
       <c r="F226">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G226">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H226">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -7167,13 +7167,13 @@
         <v>92.09996218681904</v>
       </c>
       <c r="F227">
-        <v>259.4</v>
+        <v>154.63</v>
       </c>
       <c r="G227">
-        <v>287.6</v>
+        <v>160.89</v>
       </c>
       <c r="H227">
-        <v>183.21</v>
+        <v>75.17</v>
       </c>
     </row>
     <row r="228">
@@ -7197,13 +7197,13 @@
         <v>92.21064939066757</v>
       </c>
       <c r="F228">
-        <v>190.83</v>
+        <v>119.32</v>
       </c>
       <c r="G228">
-        <v>266.32</v>
+        <v>112.94</v>
       </c>
       <c r="H228">
-        <v>207.47</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="229">
@@ -7227,13 +7227,13 @@
         <v>92.31999017626677</v>
       </c>
       <c r="F229">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G229">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H229">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="230">
@@ -7257,13 +7257,13 @@
         <v>92.42833602381741</v>
       </c>
       <c r="F230">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G230">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H230">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="231">
@@ -7287,13 +7287,13 @@
         <v>92.53624044544664</v>
       </c>
       <c r="F231">
-        <v>261.55</v>
+        <v>181.8</v>
       </c>
       <c r="G231">
-        <v>312.36</v>
+        <v>129.63</v>
       </c>
       <c r="H231">
-        <v>262.78</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="232">
@@ -7317,13 +7317,13 @@
         <v>92.64341423106801</v>
       </c>
       <c r="F232">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G232">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H232">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="233">
@@ -7347,13 +7347,13 @@
         <v>92.74960968400462</v>
       </c>
       <c r="F233">
-        <v>160.52</v>
+        <v>113.96</v>
       </c>
       <c r="G233">
-        <v>254.62</v>
+        <v>57.24</v>
       </c>
       <c r="H233">
-        <v>251.13</v>
+        <v>66.70999999999999</v>
       </c>
     </row>
     <row r="234">
@@ -7377,13 +7377,13 @@
         <v>92.85534433809539</v>
       </c>
       <c r="F234">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G234">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H234">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="235">
@@ -7407,13 +7407,13 @@
         <v>92.9587860681994</v>
       </c>
       <c r="F235">
-        <v>378.85</v>
+        <v>173.21</v>
       </c>
       <c r="G235">
-        <v>388.17</v>
+        <v>189.41</v>
       </c>
       <c r="H235">
-        <v>271.93</v>
+        <v>161.08</v>
       </c>
     </row>
     <row r="236">
@@ -7437,13 +7437,13 @@
         <v>93.0607125588553</v>
       </c>
       <c r="F236">
-        <v>267.07</v>
+        <v>180.65</v>
       </c>
       <c r="G236">
-        <v>258.51</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="H236">
-        <v>216.15</v>
+        <v>118.16</v>
       </c>
     </row>
     <row r="237">
@@ -7467,13 +7467,13 @@
         <v>93.16253388220703</v>
       </c>
       <c r="F237">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G237">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H237">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="238">
@@ -7497,13 +7497,13 @@
         <v>93.26399265511547</v>
       </c>
       <c r="F238">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G238">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H238">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="239">
@@ -7527,13 +7527,13 @@
         <v>93.36369125945957</v>
       </c>
       <c r="F239">
-        <v>233.44</v>
+        <v>146.62</v>
       </c>
       <c r="G239">
-        <v>283.03</v>
+        <v>143.19</v>
       </c>
       <c r="H239">
-        <v>204.96</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="240">
@@ -7557,13 +7557,13 @@
         <v>93.46270074120532</v>
       </c>
       <c r="F240">
-        <v>175.84</v>
+        <v>129.29</v>
       </c>
       <c r="G240">
-        <v>265.48</v>
+        <v>66.03999999999999</v>
       </c>
       <c r="H240">
-        <v>278.93</v>
+        <v>64.32000000000001</v>
       </c>
     </row>
     <row r="241">
@@ -7587,13 +7587,13 @@
         <v>93.56126049434778</v>
       </c>
       <c r="F241">
-        <v>216.88</v>
+        <v>114.21</v>
       </c>
       <c r="G241">
-        <v>257.94</v>
+        <v>103.81</v>
       </c>
       <c r="H241">
-        <v>206.2</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="242">
@@ -7617,13 +7617,13 @@
         <v>93.65799780881156</v>
       </c>
       <c r="F242">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G242">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H242">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="243">
@@ -7647,13 +7647,13 @@
         <v>93.75213638383831</v>
       </c>
       <c r="F243">
-        <v>265.33</v>
+        <v>176.55</v>
       </c>
       <c r="G243">
-        <v>303.56</v>
+        <v>131.22</v>
       </c>
       <c r="H243">
-        <v>258.37</v>
+        <v>93.84999999999999</v>
       </c>
     </row>
     <row r="244">
@@ -7677,13 +7677,13 @@
         <v>93.84561074431247</v>
       </c>
       <c r="F244">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G244">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H244">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="245">
@@ -7707,13 +7707,13 @@
         <v>93.93892597005008</v>
       </c>
       <c r="F245">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G245">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H245">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="246">
@@ -7737,13 +7737,13 @@
         <v>94.03121027945085</v>
       </c>
       <c r="F246">
-        <v>322.79</v>
+        <v>230.49</v>
       </c>
       <c r="G246">
-        <v>285.41</v>
+        <v>165.36</v>
       </c>
       <c r="H246">
-        <v>207.02</v>
+        <v>96.02</v>
       </c>
     </row>
     <row r="247">
@@ -7767,13 +7767,13 @@
         <v>94.1232538110763</v>
       </c>
       <c r="F247">
-        <v>188.1</v>
+        <v>124.25</v>
       </c>
       <c r="G247">
-        <v>274.87</v>
+        <v>104.93</v>
       </c>
       <c r="H247">
-        <v>234.11</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="248">
@@ -7797,13 +7797,13 @@
         <v>94.21210081016741</v>
       </c>
       <c r="F248">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G248">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H248">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="249">
@@ -7827,13 +7827,13 @@
         <v>94.30025453531925</v>
       </c>
       <c r="F249">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G249">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H249">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="250">
@@ -7857,13 +7857,13 @@
         <v>94.38754063021176</v>
       </c>
       <c r="F250">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G250">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H250">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="251">
@@ -7887,13 +7887,13 @@
         <v>94.47477414145219</v>
       </c>
       <c r="F251">
-        <v>224.83</v>
+        <v>123.05</v>
       </c>
       <c r="G251">
-        <v>294.84</v>
+        <v>112.63</v>
       </c>
       <c r="H251">
-        <v>235.34</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="252">
@@ -7917,13 +7917,13 @@
         <v>94.56195230147991</v>
       </c>
       <c r="F252">
-        <v>190.83</v>
+        <v>119.32</v>
       </c>
       <c r="G252">
-        <v>266.32</v>
+        <v>112.94</v>
       </c>
       <c r="H252">
-        <v>207.47</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="253">
@@ -7947,13 +7947,13 @@
         <v>94.64901837530186</v>
       </c>
       <c r="F253">
-        <v>188.1</v>
+        <v>124.25</v>
       </c>
       <c r="G253">
-        <v>274.87</v>
+        <v>104.93</v>
       </c>
       <c r="H253">
-        <v>234.11</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="254">
@@ -7977,13 +7977,13 @@
         <v>94.73492760877808</v>
       </c>
       <c r="F254">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G254">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H254">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="255">
@@ -8007,13 +8007,13 @@
         <v>94.82011312514803</v>
       </c>
       <c r="F255">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G255">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H255">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="256">
@@ -8037,13 +8037,13 @@
         <v>94.90488627498323</v>
       </c>
       <c r="F256">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G256">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H256">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="257">
@@ -8067,13 +8067,13 @@
         <v>94.98658743251269</v>
       </c>
       <c r="F257">
-        <v>261.55</v>
+        <v>181.8</v>
       </c>
       <c r="G257">
-        <v>312.36</v>
+        <v>129.63</v>
       </c>
       <c r="H257">
-        <v>262.78</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="258">
@@ -8097,13 +8097,13 @@
         <v>95.06816128225292</v>
       </c>
       <c r="F258">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G258">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H258">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -8127,13 +8127,13 @@
         <v>95.14853124311657</v>
       </c>
       <c r="F259">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G259">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H259">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="260">
@@ -8157,13 +8157,13 @@
         <v>95.22788135788591</v>
       </c>
       <c r="F260">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G260">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H260">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="261">
@@ -8187,13 +8187,13 @@
         <v>95.3063666099566</v>
       </c>
       <c r="F261">
-        <v>261.55</v>
+        <v>181.8</v>
       </c>
       <c r="G261">
-        <v>312.36</v>
+        <v>129.63</v>
       </c>
       <c r="H261">
-        <v>262.78</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="262">
@@ -8217,13 +8217,13 @@
         <v>95.3839039725095</v>
       </c>
       <c r="F262">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G262">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H262">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="263">
@@ -8247,13 +8247,13 @@
         <v>95.46061245065196</v>
       </c>
       <c r="F263">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G263">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H263">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="264">
@@ -8277,13 +8277,13 @@
         <v>95.53553170084342</v>
       </c>
       <c r="F264">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G264">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H264">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="265">
@@ -8307,13 +8307,13 @@
         <v>95.60998184950709</v>
       </c>
       <c r="F265">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G265">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H265">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="266">
@@ -8337,13 +8337,13 @@
         <v>95.6838632644601</v>
       </c>
       <c r="F266">
-        <v>322.79</v>
+        <v>230.49</v>
       </c>
       <c r="G266">
-        <v>285.41</v>
+        <v>165.36</v>
       </c>
       <c r="H266">
-        <v>207.02</v>
+        <v>96.02</v>
       </c>
     </row>
     <row r="267">
@@ -8367,13 +8367,13 @@
         <v>95.75546005810827</v>
       </c>
       <c r="F267">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G267">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H267">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="268">
@@ -8397,13 +8397,13 @@
         <v>95.82704301395324</v>
       </c>
       <c r="F268">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G268">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H268">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="269">
@@ -8427,13 +8427,13 @@
         <v>95.89764902089379</v>
       </c>
       <c r="F269">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G269">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H269">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="270">
@@ -8457,13 +8457,13 @@
         <v>95.96725870600544</v>
       </c>
       <c r="F270">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G270">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H270">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="271">
@@ -8487,13 +8487,13 @@
         <v>96.03598277171365</v>
       </c>
       <c r="F271">
-        <v>293.58</v>
+        <v>150.62</v>
       </c>
       <c r="G271">
-        <v>316.07</v>
+        <v>151.76</v>
       </c>
       <c r="H271">
-        <v>223.42</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="272">
@@ -8517,13 +8517,13 @@
         <v>96.1037990775333</v>
       </c>
       <c r="F272">
-        <v>175.84</v>
+        <v>129.29</v>
       </c>
       <c r="G272">
-        <v>265.48</v>
+        <v>66.03999999999999</v>
       </c>
       <c r="H272">
-        <v>278.93</v>
+        <v>64.32000000000001</v>
       </c>
     </row>
     <row r="273">
@@ -8547,13 +8547,13 @@
         <v>96.17027865156587</v>
       </c>
       <c r="F273">
-        <v>261.55</v>
+        <v>181.8</v>
       </c>
       <c r="G273">
-        <v>312.36</v>
+        <v>129.63</v>
       </c>
       <c r="H273">
-        <v>262.78</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="274">
@@ -8577,13 +8577,13 @@
         <v>96.23669042036286</v>
       </c>
       <c r="F274">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G274">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H274">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="275">
@@ -8607,13 +8607,13 @@
         <v>96.30276316298195</v>
       </c>
       <c r="F275">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G275">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H275">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="276">
@@ -8637,13 +8637,13 @@
         <v>96.36847750649873</v>
       </c>
       <c r="F276">
-        <v>260.87</v>
+        <v>165.97</v>
       </c>
       <c r="G276">
-        <v>276.28</v>
+        <v>140.74</v>
       </c>
       <c r="H276">
-        <v>219.23</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="277">
@@ -8667,13 +8667,13 @@
         <v>96.43355669484957</v>
       </c>
       <c r="F277">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G277">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H277">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="278">
@@ -8697,13 +8697,13 @@
         <v>96.49727147580697</v>
       </c>
       <c r="F278">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G278">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H278">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="279">
@@ -8727,13 +8727,13 @@
         <v>96.5594585632934</v>
       </c>
       <c r="F279">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G279">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H279">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="280">
@@ -8757,13 +8757,13 @@
         <v>96.62127618143498</v>
       </c>
       <c r="F280">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G280">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H280">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="281">
@@ -8787,13 +8787,13 @@
         <v>96.6828986865517</v>
       </c>
       <c r="F281">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G281">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H281">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="282">
@@ -8817,13 +8817,13 @@
         <v>96.74421675999851</v>
       </c>
       <c r="F282">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G282">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H282">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="283">
@@ -8847,13 +8847,13 @@
         <v>96.80538261761033</v>
       </c>
       <c r="F283">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G283">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H283">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="284">
@@ -8877,13 +8877,13 @@
         <v>96.86401754102071</v>
       </c>
       <c r="F284">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G284">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H284">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="285">
@@ -8907,13 +8907,13 @@
         <v>96.92228991398783</v>
       </c>
       <c r="F285">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G285">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H285">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="286">
@@ -8937,13 +8937,13 @@
         <v>96.98014576907923</v>
       </c>
       <c r="F286">
-        <v>300.53</v>
+        <v>212.24</v>
       </c>
       <c r="G286">
-        <v>261.6</v>
+        <v>130.98</v>
       </c>
       <c r="H286">
-        <v>194.14</v>
+        <v>90.41</v>
       </c>
     </row>
     <row r="287">
@@ -8967,13 +8967,13 @@
         <v>97.037937970276</v>
       </c>
       <c r="F287">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G287">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H287">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="288">
@@ -8997,13 +8997,13 @@
         <v>97.09562500416864</v>
       </c>
       <c r="F288">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G288">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H288">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="289">
@@ -9027,13 +9027,13 @@
         <v>97.15329958403841</v>
       </c>
       <c r="F289">
-        <v>270.89</v>
+        <v>133.65</v>
       </c>
       <c r="G289">
-        <v>321.03</v>
+        <v>160.34</v>
       </c>
       <c r="H289">
-        <v>229.65</v>
+        <v>104.81</v>
       </c>
     </row>
     <row r="290">
@@ -9057,13 +9057,13 @@
         <v>97.21063375394998</v>
       </c>
       <c r="F290">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G290">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H290">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="291">
@@ -9087,13 +9087,13 @@
         <v>97.26783923229196</v>
       </c>
       <c r="F291">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G291">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H291">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="292">
@@ -9117,13 +9117,13 @@
         <v>97.32430162060325</v>
       </c>
       <c r="F292">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G292">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H292">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="293">
@@ -9147,13 +9147,13 @@
         <v>97.37968881160754</v>
       </c>
       <c r="F293">
-        <v>299.22</v>
+        <v>247.43</v>
       </c>
       <c r="G293">
-        <v>159.03</v>
+        <v>60.56</v>
       </c>
       <c r="H293">
-        <v>190.48</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="294">
@@ -9177,13 +9177,13 @@
         <v>97.43488227336729</v>
       </c>
       <c r="F294">
-        <v>250.37</v>
+        <v>179.21</v>
       </c>
       <c r="G294">
-        <v>293.61</v>
+        <v>147.98</v>
       </c>
       <c r="H294">
-        <v>231.59</v>
+        <v>92.13000000000001</v>
       </c>
     </row>
     <row r="295">
@@ -9207,13 +9207,13 @@
         <v>97.48972148736568</v>
       </c>
       <c r="F295">
-        <v>175.84</v>
+        <v>129.29</v>
       </c>
       <c r="G295">
-        <v>265.48</v>
+        <v>66.03999999999999</v>
       </c>
       <c r="H295">
-        <v>278.93</v>
+        <v>64.32000000000001</v>
       </c>
     </row>
     <row r="296">
@@ -9237,13 +9237,13 @@
         <v>97.54443616113547</v>
       </c>
       <c r="F296">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G296">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H296">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="297">
@@ -9267,13 +9267,13 @@
         <v>97.59773937898099</v>
       </c>
       <c r="F297">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G297">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H297">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="298">
@@ -9297,13 +9297,13 @@
         <v>97.64979719454038</v>
       </c>
       <c r="F298">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G298">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H298">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="299">
@@ -9327,13 +9327,13 @@
         <v>97.70152151904318</v>
       </c>
       <c r="F299">
-        <v>181.09</v>
+        <v>130.13</v>
       </c>
       <c r="G299">
-        <v>207.07</v>
+        <v>58.12</v>
       </c>
       <c r="H299">
-        <v>224.76</v>
+        <v>57.47</v>
       </c>
     </row>
     <row r="300">
@@ -9357,13 +9357,13 @@
         <v>97.75320571391677</v>
       </c>
       <c r="F300">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G300">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H300">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="301">
@@ -9387,13 +9387,13 @@
         <v>97.80364450650423</v>
       </c>
       <c r="F301">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G301">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H301">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="302">
@@ -9417,13 +9417,13 @@
         <v>97.85385912668019</v>
       </c>
       <c r="F302">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G302">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H302">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="303">
@@ -9447,13 +9447,13 @@
         <v>97.90223885415462</v>
       </c>
       <c r="F303">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G303">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H303">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="304">
@@ -9477,13 +9477,13 @@
         <v>97.95061027894715</v>
       </c>
       <c r="F304">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G304">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H304">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="305">
@@ -9507,13 +9507,13 @@
         <v>97.99785669034121</v>
       </c>
       <c r="F305">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G305">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H305">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="306">
@@ -9537,13 +9537,13 @@
         <v>98.04492459407427</v>
       </c>
       <c r="F306">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G306">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H306">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="307">
@@ -9567,13 +9567,13 @@
         <v>98.09195513573876</v>
       </c>
       <c r="F307">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G307">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H307">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="308">
@@ -9597,13 +9597,13 @@
         <v>98.13827441431982</v>
       </c>
       <c r="F308">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G308">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H308">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="309">
@@ -9627,13 +9627,13 @@
         <v>98.18061670826727</v>
       </c>
       <c r="F309">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G309">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H309">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="310">
@@ -9657,13 +9657,13 @@
         <v>98.22176064845939</v>
       </c>
       <c r="F310">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G310">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H310">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="311">
@@ -9687,13 +9687,13 @@
         <v>98.26288383194675</v>
       </c>
       <c r="F311">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G311">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H311">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="312">
@@ -9717,13 +9717,13 @@
         <v>98.30378007546197</v>
       </c>
       <c r="F312">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G312">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H312">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="313">
@@ -9747,13 +9747,13 @@
         <v>98.34449642753586</v>
       </c>
       <c r="F313">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G313">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H313">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="314">
@@ -9777,13 +9777,13 @@
         <v>98.38428979813773</v>
       </c>
       <c r="F314">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G314">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H314">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="315">
@@ -9807,13 +9807,13 @@
         <v>98.4232957977387</v>
       </c>
       <c r="F315">
-        <v>189.55</v>
+        <v>122.68</v>
       </c>
       <c r="G315">
-        <v>260.92</v>
+        <v>75.19</v>
       </c>
       <c r="H315">
-        <v>231</v>
+        <v>93.14999999999999</v>
       </c>
     </row>
     <row r="316">
@@ -9837,13 +9837,13 @@
         <v>98.45824870478856</v>
       </c>
       <c r="F316">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G316">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H316">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="317">
@@ -9867,13 +9867,13 @@
         <v>98.49308814185233</v>
       </c>
       <c r="F317">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G317">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H317">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="318">
@@ -9897,13 +9897,13 @@
         <v>98.52696308403452</v>
       </c>
       <c r="F318">
-        <v>220.96</v>
+        <v>141.04</v>
       </c>
       <c r="G318">
-        <v>263.36</v>
+        <v>77.72</v>
       </c>
       <c r="H318">
-        <v>225.98</v>
+        <v>113.83</v>
       </c>
     </row>
     <row r="319">
@@ -9927,13 +9927,13 @@
         <v>98.56080481548909</v>
       </c>
       <c r="F319">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G319">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H319">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="320">
@@ -9957,13 +9957,13 @@
         <v>98.59460918487508</v>
       </c>
       <c r="F320">
-        <v>172.92</v>
+        <v>130.11</v>
       </c>
       <c r="G320">
-        <v>237.57</v>
+        <v>58.73</v>
       </c>
       <c r="H320">
-        <v>264.33</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="321">
@@ -9987,13 +9987,13 @@
         <v>98.62729684354451</v>
       </c>
       <c r="F321">
-        <v>378.85</v>
+        <v>173.21</v>
       </c>
       <c r="G321">
-        <v>388.17</v>
+        <v>189.41</v>
       </c>
       <c r="H321">
-        <v>271.93</v>
+        <v>161.08</v>
       </c>
     </row>
     <row r="322">
@@ -10017,13 +10017,13 @@
         <v>98.65981568101517</v>
       </c>
       <c r="F322">
-        <v>459.81</v>
+        <v>205.57</v>
       </c>
       <c r="G322">
-        <v>440.54</v>
+        <v>199.15</v>
       </c>
       <c r="H322">
-        <v>315.3</v>
+        <v>222.74</v>
       </c>
     </row>
     <row r="323">
@@ -10047,13 +10047,13 @@
         <v>98.69195951401967</v>
       </c>
       <c r="F323">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G323">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H323">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="324">
@@ -10077,13 +10077,13 @@
         <v>98.72345158649445</v>
       </c>
       <c r="F324">
-        <v>339.8</v>
+        <v>251</v>
       </c>
       <c r="G324">
-        <v>339.08</v>
+        <v>164.39</v>
       </c>
       <c r="H324">
-        <v>261.08</v>
+        <v>68.92</v>
       </c>
     </row>
     <row r="325">
@@ -10107,13 +10107,13 @@
         <v>98.75473609192153</v>
       </c>
       <c r="F325">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G325">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H325">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="326">
@@ -10137,13 +10137,13 @@
         <v>98.78548507436561</v>
       </c>
       <c r="F326">
-        <v>271.67</v>
+        <v>147.56</v>
       </c>
       <c r="G326">
-        <v>308.19</v>
+        <v>170.14</v>
       </c>
       <c r="H326">
-        <v>197.49</v>
+        <v>90</v>
       </c>
     </row>
     <row r="327">
@@ -10167,13 +10167,13 @@
         <v>98.81583137673717</v>
       </c>
       <c r="F327">
-        <v>300.53</v>
+        <v>212.24</v>
       </c>
       <c r="G327">
-        <v>261.6</v>
+        <v>130.98</v>
       </c>
       <c r="H327">
-        <v>194.14</v>
+        <v>90.41</v>
       </c>
     </row>
     <row r="328">
@@ -10197,13 +10197,13 @@
         <v>98.8457210316038</v>
       </c>
       <c r="F328">
-        <v>254.03</v>
+        <v>168.85</v>
       </c>
       <c r="G328">
-        <v>255.53</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="H328">
-        <v>213.38</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="329">
@@ -10227,13 +10227,13 @@
         <v>98.87506409324487</v>
       </c>
       <c r="F329">
-        <v>172.92</v>
+        <v>130.11</v>
       </c>
       <c r="G329">
-        <v>237.57</v>
+        <v>58.73</v>
       </c>
       <c r="H329">
-        <v>264.33</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="330">
@@ -10257,13 +10257,13 @@
         <v>98.90379137264449</v>
       </c>
       <c r="F330">
-        <v>175.84</v>
+        <v>129.29</v>
       </c>
       <c r="G330">
-        <v>265.48</v>
+        <v>66.03999999999999</v>
       </c>
       <c r="H330">
-        <v>278.93</v>
+        <v>64.32000000000001</v>
       </c>
     </row>
     <row r="331">
@@ -10287,13 +10287,13 @@
         <v>98.93234429572404</v>
       </c>
       <c r="F331">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G331">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H331">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="332">
@@ -10317,13 +10317,13 @@
         <v>98.96081695954516</v>
       </c>
       <c r="F332">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G332">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H332">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="333">
@@ -10347,13 +10347,13 @@
         <v>98.98814385326305</v>
       </c>
       <c r="F333">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G333">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H333">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="334">
@@ -10377,13 +10377,13 @@
         <v>99.01518707201578</v>
       </c>
       <c r="F334">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G334">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H334">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="335">
@@ -10407,13 +10407,13 @@
         <v>99.0420988316383</v>
       </c>
       <c r="F335">
-        <v>321.12</v>
+        <v>235.82</v>
       </c>
       <c r="G335">
-        <v>317.12</v>
+        <v>148.4</v>
       </c>
       <c r="H335">
-        <v>240.4</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="336">
@@ -10437,13 +10437,13 @@
         <v>99.06858853826388</v>
       </c>
       <c r="F336">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G336">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H336">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="337">
@@ -10467,13 +10467,13 @@
         <v>99.09488036430399</v>
       </c>
       <c r="F337">
-        <v>360.92</v>
+        <v>310.95</v>
       </c>
       <c r="G337">
-        <v>170.24</v>
+        <v>62.47</v>
       </c>
       <c r="H337">
-        <v>190.14</v>
+        <v>53.15</v>
       </c>
     </row>
     <row r="338">
@@ -10497,13 +10497,13 @@
         <v>99.12009007413548</v>
       </c>
       <c r="F338">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G338">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H338">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="339">
@@ -10527,13 +10527,13 @@
         <v>99.14465909367979</v>
       </c>
       <c r="F339">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G339">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H339">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="340">
@@ -10557,13 +10557,13 @@
         <v>99.16899978947167</v>
       </c>
       <c r="F340">
-        <v>270.89</v>
+        <v>133.65</v>
       </c>
       <c r="G340">
-        <v>321.03</v>
+        <v>160.34</v>
       </c>
       <c r="H340">
-        <v>229.65</v>
+        <v>104.81</v>
       </c>
     </row>
     <row r="341">
@@ -10587,13 +10587,13 @@
         <v>99.19325053954287</v>
       </c>
       <c r="F341">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G341">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H341">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="342">
@@ -10617,13 +10617,13 @@
         <v>99.21725912805844</v>
       </c>
       <c r="F342">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G342">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H342">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="343">
@@ -10647,13 +10647,13 @@
         <v>99.24109612781459</v>
       </c>
       <c r="F343">
-        <v>282.22</v>
+        <v>182.6</v>
       </c>
       <c r="G343">
-        <v>287.05</v>
+        <v>160.36</v>
       </c>
       <c r="H343">
-        <v>192.31</v>
+        <v>85.48</v>
       </c>
     </row>
     <row r="344">
@@ -10677,13 +10677,13 @@
         <v>99.26427583191975</v>
       </c>
       <c r="F344">
-        <v>224.83</v>
+        <v>123.05</v>
       </c>
       <c r="G344">
-        <v>294.84</v>
+        <v>112.63</v>
       </c>
       <c r="H344">
-        <v>235.34</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="345">
@@ -10707,13 +10707,13 @@
         <v>99.28745415224456</v>
       </c>
       <c r="F345">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G345">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H345">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="346">
@@ -10737,13 +10737,13 @@
         <v>99.31039169479409</v>
       </c>
       <c r="F346">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G346">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H346">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="347">
@@ -10767,13 +10767,13 @@
         <v>99.33250450427413</v>
       </c>
       <c r="F347">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G347">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H347">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="348">
@@ -10797,13 +10797,13 @@
         <v>99.35450107620747</v>
       </c>
       <c r="F348">
-        <v>322.79</v>
+        <v>230.49</v>
       </c>
       <c r="G348">
-        <v>285.41</v>
+        <v>165.36</v>
       </c>
       <c r="H348">
-        <v>207.02</v>
+        <v>96.02</v>
       </c>
     </row>
     <row r="349">
@@ -10827,13 +10827,13 @@
         <v>99.37573380140533</v>
       </c>
       <c r="F349">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G349">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H349">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="350">
@@ -10857,13 +10857,13 @@
         <v>99.39640747935476</v>
       </c>
       <c r="F350">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G350">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H350">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="351">
@@ -10887,13 +10887,13 @@
         <v>99.41706731950102</v>
       </c>
       <c r="F351">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G351">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H351">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="352">
@@ -10917,13 +10917,13 @@
         <v>99.43759985185801</v>
       </c>
       <c r="F352">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G352">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H352">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="353">
@@ -10947,13 +10947,13 @@
         <v>99.45709870031756</v>
       </c>
       <c r="F353">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G353">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H353">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="354">
@@ -10977,13 +10977,13 @@
         <v>99.4765366624431</v>
       </c>
       <c r="F354">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G354">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H354">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="355">
@@ -11007,13 +11007,13 @@
         <v>99.49557056071581</v>
       </c>
       <c r="F355">
-        <v>224.83</v>
+        <v>123.05</v>
       </c>
       <c r="G355">
-        <v>294.84</v>
+        <v>112.63</v>
       </c>
       <c r="H355">
-        <v>235.34</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="356">
@@ -11037,13 +11037,13 @@
         <v>99.51398175784547</v>
       </c>
       <c r="F356">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G356">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H356">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="357">
@@ -11067,13 +11067,13 @@
         <v>99.53231546327734</v>
       </c>
       <c r="F357">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G357">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H357">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="358">
@@ -11097,13 +11097,13 @@
         <v>99.54946050141612</v>
       </c>
       <c r="F358">
-        <v>287.84</v>
+        <v>200.74</v>
       </c>
       <c r="G358">
-        <v>278.73</v>
+        <v>162.03</v>
       </c>
       <c r="H358">
-        <v>198.28</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="359">
@@ -11127,13 +11127,13 @@
         <v>99.56611152998141</v>
       </c>
       <c r="F359">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G359">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H359">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="360">
@@ -11157,13 +11157,13 @@
         <v>99.58209419265316</v>
       </c>
       <c r="F360">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G360">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H360">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="361">
@@ -11187,13 +11187,13 @@
         <v>99.59711789556461</v>
       </c>
       <c r="F361">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G361">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H361">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="362">
@@ -11217,13 +11217,13 @@
         <v>99.61207932836174</v>
       </c>
       <c r="F362">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G362">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H362">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="363">
@@ -11247,13 +11247,13 @@
         <v>99.62650247061522</v>
       </c>
       <c r="F363">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G363">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H363">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="364">
@@ -11277,13 +11277,13 @@
         <v>99.64082736446613</v>
       </c>
       <c r="F364">
-        <v>300.53</v>
+        <v>212.24</v>
       </c>
       <c r="G364">
-        <v>261.6</v>
+        <v>130.98</v>
       </c>
       <c r="H364">
-        <v>194.14</v>
+        <v>90.41</v>
       </c>
     </row>
     <row r="365">
@@ -11307,13 +11307,13 @@
         <v>99.65461535155367</v>
       </c>
       <c r="F365">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G365">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H365">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="366">
@@ -11337,13 +11337,13 @@
         <v>99.66719668220404</v>
       </c>
       <c r="F366">
-        <v>185.75</v>
+        <v>72.92</v>
       </c>
       <c r="G366">
-        <v>245.12</v>
+        <v>104.09</v>
       </c>
       <c r="H366">
-        <v>206.2</v>
+        <v>112.06</v>
       </c>
     </row>
     <row r="367">
@@ -11367,13 +11367,13 @@
         <v>99.67906951733163</v>
       </c>
       <c r="F367">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G367">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H367">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="368">
@@ -11397,13 +11397,13 @@
         <v>99.69063930456959</v>
       </c>
       <c r="F368">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G368">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H368">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="369">
@@ -11427,13 +11427,13 @@
         <v>99.70219387022405</v>
       </c>
       <c r="F369">
-        <v>285.31</v>
+        <v>134.69</v>
       </c>
       <c r="G369">
-        <v>321.57</v>
+        <v>139.51</v>
       </c>
       <c r="H369">
-        <v>244.65</v>
+        <v>134.49</v>
       </c>
     </row>
     <row r="370">
@@ -11457,13 +11457,13 @@
         <v>99.71358238224038</v>
       </c>
       <c r="F370">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G370">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H370">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="371">
@@ -11487,13 +11487,13 @@
         <v>99.72486434317221</v>
       </c>
       <c r="F371">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G371">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H371">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="372">
@@ -11517,13 +11517,13 @@
         <v>99.73610479069451</v>
       </c>
       <c r="F372">
-        <v>250.77</v>
+        <v>145.79</v>
       </c>
       <c r="G372">
-        <v>290.31</v>
+        <v>166.16</v>
       </c>
       <c r="H372">
-        <v>178.89</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="373">
@@ -11547,13 +11547,13 @@
         <v>99.74706986593355</v>
       </c>
       <c r="F373">
-        <v>175.84</v>
+        <v>129.29</v>
       </c>
       <c r="G373">
-        <v>265.48</v>
+        <v>66.03999999999999</v>
       </c>
       <c r="H373">
-        <v>278.93</v>
+        <v>64.32000000000001</v>
       </c>
     </row>
     <row r="374">
@@ -11577,13 +11577,13 @@
         <v>99.75759213147086</v>
       </c>
       <c r="F374">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G374">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H374">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="375">
@@ -11607,13 +11607,13 @@
         <v>99.76758025780546</v>
       </c>
       <c r="F375">
-        <v>297.18</v>
+        <v>142.39</v>
       </c>
       <c r="G375">
-        <v>339.25</v>
+        <v>155.15</v>
       </c>
       <c r="H375">
-        <v>247.15</v>
+        <v>130.83</v>
       </c>
     </row>
     <row r="376">
@@ -11637,13 +11637,13 @@
         <v>99.77745214659338</v>
       </c>
       <c r="F376">
-        <v>254.03</v>
+        <v>168.85</v>
       </c>
       <c r="G376">
-        <v>255.53</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="H376">
-        <v>213.38</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="377">
@@ -11667,13 +11667,13 @@
         <v>99.78729774355524</v>
       </c>
       <c r="F377">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G377">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H377">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="378">
@@ -11697,13 +11697,13 @@
         <v>99.79710874600914</v>
       </c>
       <c r="F378">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G378">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H378">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="379">
@@ -11727,13 +11727,13 @@
         <v>99.80686439725035</v>
       </c>
       <c r="F379">
-        <v>275.03</v>
+        <v>191.06</v>
       </c>
       <c r="G379">
-        <v>268.12</v>
+        <v>127.29</v>
       </c>
       <c r="H379">
-        <v>215.34</v>
+        <v>82.56</v>
       </c>
     </row>
     <row r="380">
@@ -11757,13 +11757,13 @@
         <v>99.8166158971506</v>
       </c>
       <c r="F380">
-        <v>290.58</v>
+        <v>205.62</v>
       </c>
       <c r="G380">
-        <v>281.58</v>
+        <v>160.06</v>
       </c>
       <c r="H380">
-        <v>207.66</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="381">
@@ -11787,13 +11787,13 @@
         <v>99.82628852157272</v>
       </c>
       <c r="F381">
-        <v>224.83</v>
+        <v>123.05</v>
       </c>
       <c r="G381">
-        <v>294.84</v>
+        <v>112.63</v>
       </c>
       <c r="H381">
-        <v>235.34</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="382">
@@ -11817,13 +11817,13 @@
         <v>99.83509074817488</v>
       </c>
       <c r="F382">
-        <v>169.6</v>
+        <v>112.92</v>
       </c>
       <c r="G382">
-        <v>256.37</v>
+        <v>84.53</v>
       </c>
       <c r="H382">
-        <v>227.28</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="383">
@@ -11847,13 +11847,13 @@
         <v>99.84346400287849</v>
       </c>
       <c r="F383">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G383">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H383">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="384">
@@ -11877,13 +11877,13 @@
         <v>99.85094887061801</v>
       </c>
       <c r="F384">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G384">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H384">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="385">
@@ -11907,13 +11907,13 @@
         <v>99.85831611703053</v>
       </c>
       <c r="F385">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G385">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H385">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="386">
@@ -11937,13 +11937,13 @@
         <v>99.86564876893507</v>
       </c>
       <c r="F386">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G386">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H386">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="387">
@@ -11967,13 +11967,13 @@
         <v>99.87254829760012</v>
       </c>
       <c r="F387">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G387">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H387">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="388">
@@ -11997,13 +11997,13 @@
         <v>99.87937725346896</v>
       </c>
       <c r="F388">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G388">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H388">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="389">
@@ -12027,13 +12027,13 @@
         <v>99.88596819912311</v>
       </c>
       <c r="F389">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G389">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H389">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="390">
@@ -12057,13 +12057,13 @@
         <v>99.89240969650294</v>
       </c>
       <c r="F390">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G390">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H390">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="391">
@@ -12087,13 +12087,13 @@
         <v>99.89853292440965</v>
       </c>
       <c r="F391">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G391">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H391">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="392">
@@ -12117,13 +12117,13 @@
         <v>99.90450532026171</v>
       </c>
       <c r="F392">
-        <v>234.52</v>
+        <v>180.91</v>
       </c>
       <c r="G392">
-        <v>169.61</v>
+        <v>87.37</v>
       </c>
       <c r="H392">
-        <v>153.98</v>
+        <v>49.66</v>
       </c>
     </row>
     <row r="393">
@@ -12147,13 +12147,13 @@
         <v>99.91041682977976</v>
       </c>
       <c r="F393">
-        <v>266.67</v>
+        <v>196.77</v>
       </c>
       <c r="G393">
-        <v>300.49</v>
+        <v>132.68</v>
       </c>
       <c r="H393">
-        <v>240.34</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="394">
@@ -12177,13 +12177,13 @@
         <v>99.91617473968256</v>
       </c>
       <c r="F394">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G394">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H394">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="395">
@@ -12207,13 +12207,13 @@
         <v>99.92152166683093</v>
       </c>
       <c r="F395">
-        <v>224.83</v>
+        <v>123.05</v>
       </c>
       <c r="G395">
-        <v>294.84</v>
+        <v>112.63</v>
       </c>
       <c r="H395">
-        <v>235.34</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="396">
@@ -12237,13 +12237,13 @@
         <v>99.92670392412147</v>
       </c>
       <c r="F396">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G396">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H396">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="397">
@@ -12267,13 +12267,13 @@
         <v>99.93158728486333</v>
       </c>
       <c r="F397">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G397">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H397">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="398">
@@ -12297,13 +12297,13 @@
         <v>99.93635164049786</v>
       </c>
       <c r="F398">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G398">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H398">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="399">
@@ -12327,13 +12327,13 @@
         <v>99.94063720814241</v>
       </c>
       <c r="F399">
-        <v>190.83</v>
+        <v>119.32</v>
       </c>
       <c r="G399">
-        <v>266.32</v>
+        <v>112.94</v>
       </c>
       <c r="H399">
-        <v>207.47</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -12357,13 +12357,13 @@
         <v>99.94485358677105</v>
       </c>
       <c r="F400">
-        <v>459.81</v>
+        <v>205.57</v>
       </c>
       <c r="G400">
-        <v>440.54</v>
+        <v>199.15</v>
       </c>
       <c r="H400">
-        <v>315.3</v>
+        <v>222.74</v>
       </c>
     </row>
     <row r="401">
@@ -12387,13 +12387,13 @@
         <v>99.94903537089174</v>
       </c>
       <c r="F401">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G401">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H401">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="402">
@@ -12417,13 +12417,13 @@
         <v>99.95312997685241</v>
       </c>
       <c r="F402">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G402">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H402">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="403">
@@ -12447,13 +12447,13 @@
         <v>99.95702531844729</v>
       </c>
       <c r="F403">
-        <v>459.81</v>
+        <v>205.57</v>
       </c>
       <c r="G403">
-        <v>440.54</v>
+        <v>199.15</v>
       </c>
       <c r="H403">
-        <v>315.3</v>
+        <v>222.74</v>
       </c>
     </row>
     <row r="404">
@@ -12477,13 +12477,13 @@
         <v>99.96089436821613</v>
       </c>
       <c r="F404">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G404">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H404">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="405">
@@ -12507,13 +12507,13 @@
         <v>99.9645710725208</v>
       </c>
       <c r="F405">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G405">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H405">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="406">
@@ -12537,13 +12537,13 @@
         <v>99.96822702012069</v>
       </c>
       <c r="F406">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G406">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H406">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="407">
@@ -12567,13 +12567,13 @@
         <v>99.97172660054467</v>
       </c>
       <c r="F407">
-        <v>224.83</v>
+        <v>123.05</v>
       </c>
       <c r="G407">
-        <v>294.84</v>
+        <v>112.63</v>
       </c>
       <c r="H407">
-        <v>235.34</v>
+        <v>113.78</v>
       </c>
     </row>
     <row r="408">
@@ -12597,13 +12597,13 @@
         <v>99.97502414904223</v>
       </c>
       <c r="F408">
-        <v>280.15</v>
+        <v>142.88</v>
       </c>
       <c r="G408">
-        <v>302.59</v>
+        <v>139.54</v>
       </c>
       <c r="H408">
-        <v>222.32</v>
+        <v>120.67</v>
       </c>
     </row>
     <row r="409">
@@ -12627,13 +12627,13 @@
         <v>99.97805462793843</v>
       </c>
       <c r="F409">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G409">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H409">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="410">
@@ -12657,13 +12657,13 @@
         <v>99.98046240569157</v>
       </c>
       <c r="F410">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G410">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H410">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="411">
@@ -12687,13 +12687,13 @@
         <v>99.98264185969227</v>
       </c>
       <c r="F411">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G411">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H411">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="412">
@@ -12717,13 +12717,13 @@
         <v>99.9844919739773</v>
       </c>
       <c r="F412">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G412">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H412">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="413">
@@ -12747,13 +12747,13 @@
         <v>99.98633516936073</v>
       </c>
       <c r="F413">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G413">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H413">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="414">
@@ -12777,13 +12777,13 @@
         <v>99.98753352311604</v>
       </c>
       <c r="F414">
-        <v>190.83</v>
+        <v>119.32</v>
       </c>
       <c r="G414">
-        <v>266.32</v>
+        <v>112.94</v>
       </c>
       <c r="H414">
-        <v>207.47</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="415">
@@ -12807,13 +12807,13 @@
         <v>99.9887291093107</v>
       </c>
       <c r="F415">
-        <v>378.85</v>
+        <v>173.21</v>
       </c>
       <c r="G415">
-        <v>388.17</v>
+        <v>189.41</v>
       </c>
       <c r="H415">
-        <v>271.93</v>
+        <v>161.08</v>
       </c>
     </row>
     <row r="416">
@@ -12837,13 +12837,13 @@
         <v>99.98992469550537</v>
       </c>
       <c r="F416">
-        <v>459.81</v>
+        <v>205.57</v>
       </c>
       <c r="G416">
-        <v>440.54</v>
+        <v>199.15</v>
       </c>
       <c r="H416">
-        <v>315.3</v>
+        <v>222.74</v>
       </c>
     </row>
     <row r="417">
@@ -12867,13 +12867,13 @@
         <v>99.99106493048733</v>
       </c>
       <c r="F417">
-        <v>459.81</v>
+        <v>205.57</v>
       </c>
       <c r="G417">
-        <v>440.54</v>
+        <v>199.15</v>
       </c>
       <c r="H417">
-        <v>315.3</v>
+        <v>222.74</v>
       </c>
     </row>
     <row r="418">
@@ -12897,13 +12897,13 @@
         <v>99.99214981425656</v>
       </c>
       <c r="F418">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G418">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H418">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="419">
@@ -12927,13 +12927,13 @@
         <v>99.99320840619976</v>
       </c>
       <c r="F419">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G419">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H419">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="420">
@@ -12957,13 +12957,13 @@
         <v>99.99410647962607</v>
       </c>
       <c r="F420">
-        <v>235.42</v>
+        <v>129.85</v>
       </c>
       <c r="G420">
-        <v>291.6</v>
+        <v>107.81</v>
       </c>
       <c r="H420">
-        <v>223.42</v>
+        <v>116</v>
       </c>
     </row>
     <row r="421">
@@ -12987,13 +12987,13 @@
         <v>99.99480113734566</v>
       </c>
       <c r="F421">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G421">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H421">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="422">
@@ -13017,13 +13017,13 @@
         <v>99.99546950323919</v>
       </c>
       <c r="F422">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G422">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H422">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="423">
@@ -13047,13 +13047,13 @@
         <v>99.99610880974608</v>
       </c>
       <c r="F423">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G423">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H423">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="424">
@@ -13077,13 +13077,13 @@
         <v>99.99673151088912</v>
       </c>
       <c r="F424">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G424">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H424">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="425">
@@ -13107,13 +13107,13 @@
         <v>99.99725734740993</v>
       </c>
       <c r="F425">
-        <v>190.83</v>
+        <v>119.32</v>
       </c>
       <c r="G425">
-        <v>266.32</v>
+        <v>112.94</v>
       </c>
       <c r="H425">
-        <v>207.47</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="426">
@@ -13137,13 +13137,13 @@
         <v>99.99777626502915</v>
       </c>
       <c r="F426">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G426">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H426">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="427">
@@ -13167,13 +13167,13 @@
         <v>99.99820800448832</v>
       </c>
       <c r="F427">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G427">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H427">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="428">
@@ -13197,13 +13197,13 @@
         <v>99.99856225224971</v>
       </c>
       <c r="F428">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G428">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H428">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="429">
@@ -13227,13 +13227,13 @@
         <v>99.99886945148029</v>
       </c>
       <c r="F429">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G429">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H429">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="430">
@@ -13257,13 +13257,13 @@
         <v>99.99911161303592</v>
       </c>
       <c r="F430">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G430">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H430">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="431">
@@ -13287,13 +13287,13 @@
         <v>99.99934962325059</v>
       </c>
       <c r="F431">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G431">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H431">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="432">
@@ -13317,13 +13317,13 @@
         <v>99.99954888761637</v>
       </c>
       <c r="F432">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G432">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H432">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="433">
@@ -13347,13 +13347,13 @@
         <v>99.99970940613323</v>
       </c>
       <c r="F433">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G433">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H433">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="434">
@@ -13377,13 +13377,13 @@
         <v>99.99984778416503</v>
       </c>
       <c r="F434">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G434">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H434">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="435">
@@ -13407,13 +13407,13 @@
         <v>99.99992112452189</v>
       </c>
       <c r="F435">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G435">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H435">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="436">
@@ -13437,13 +13437,13 @@
         <v>99.99995848659047</v>
       </c>
       <c r="F436">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G436">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H436">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="437">
@@ -13467,13 +13467,13 @@
         <v>99.99999308109841</v>
       </c>
       <c r="F437">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G437">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H437">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="438">
@@ -13497,13 +13497,13 @@
         <v>99.99999723243937</v>
       </c>
       <c r="F438">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G438">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H438">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="439">
@@ -13527,13 +13527,13 @@
         <v>100</v>
       </c>
       <c r="F439">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G439">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H439">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="440">
@@ -13557,13 +13557,13 @@
         <v>100</v>
       </c>
       <c r="F440">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G440">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H440">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="441">
@@ -13587,13 +13587,13 @@
         <v>100</v>
       </c>
       <c r="F441">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G441">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H441">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="442">
@@ -13617,13 +13617,13 @@
         <v>100</v>
       </c>
       <c r="F442">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G442">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H442">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="443">
@@ -13647,13 +13647,13 @@
         <v>100</v>
       </c>
       <c r="F443">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G443">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H443">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="444">
@@ -13677,13 +13677,13 @@
         <v>100</v>
       </c>
       <c r="F444">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G444">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H444">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="445">
@@ -13707,13 +13707,13 @@
         <v>100</v>
       </c>
       <c r="F445">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G445">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H445">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="446">
@@ -13737,13 +13737,13 @@
         <v>100</v>
       </c>
       <c r="F446">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G446">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H446">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="447">
@@ -13767,13 +13767,13 @@
         <v>100</v>
       </c>
       <c r="F447">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G447">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H447">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="448">
@@ -13797,13 +13797,13 @@
         <v>100</v>
       </c>
       <c r="F448">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G448">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H448">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="449">
@@ -13827,13 +13827,13 @@
         <v>100</v>
       </c>
       <c r="F449">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G449">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H449">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="450">
@@ -13857,13 +13857,13 @@
         <v>100</v>
       </c>
       <c r="F450">
-        <v>178.71</v>
+        <v>113.42</v>
       </c>
       <c r="G450">
-        <v>264.66</v>
+        <v>94.51000000000001</v>
       </c>
       <c r="H450">
-        <v>224.99</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="451">
@@ -13887,13 +13887,13 @@
         <v>100</v>
       </c>
       <c r="F451">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G451">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H451">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="452">
@@ -13917,13 +13917,13 @@
         <v>100</v>
       </c>
       <c r="F452">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G452">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H452">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="453">
@@ -13947,13 +13947,13 @@
         <v>100</v>
       </c>
       <c r="F453">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G453">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H453">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="454">
@@ -13977,13 +13977,13 @@
         <v>100</v>
       </c>
       <c r="F454">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G454">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H454">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="455">
@@ -14007,13 +14007,13 @@
         <v>100</v>
       </c>
       <c r="F455">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G455">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H455">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="456">
@@ -14037,13 +14037,13 @@
         <v>100</v>
       </c>
       <c r="F456">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G456">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H456">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="457">
@@ -14067,13 +14067,13 @@
         <v>100</v>
       </c>
       <c r="F457">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G457">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H457">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="458">
@@ -14097,13 +14097,13 @@
         <v>100</v>
       </c>
       <c r="F458">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G458">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H458">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="459">
@@ -14127,13 +14127,13 @@
         <v>100</v>
       </c>
       <c r="F459">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G459">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H459">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="460">
@@ -14157,13 +14157,13 @@
         <v>100</v>
       </c>
       <c r="F460">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G460">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H460">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="461">
@@ -14187,13 +14187,13 @@
         <v>100</v>
       </c>
       <c r="F461">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G461">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H461">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="462">
@@ -14217,13 +14217,13 @@
         <v>100</v>
       </c>
       <c r="F462">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G462">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H462">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="463">
@@ -14247,13 +14247,13 @@
         <v>100</v>
       </c>
       <c r="F463">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G463">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H463">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="464">
@@ -14277,13 +14277,13 @@
         <v>100</v>
       </c>
       <c r="F464">
-        <v>459.81</v>
+        <v>205.57</v>
       </c>
       <c r="G464">
-        <v>440.54</v>
+        <v>199.15</v>
       </c>
       <c r="H464">
-        <v>315.3</v>
+        <v>222.74</v>
       </c>
     </row>
     <row r="465">
@@ -14307,13 +14307,13 @@
         <v>100</v>
       </c>
       <c r="F465">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G465">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H465">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="466">
@@ -14337,13 +14337,13 @@
         <v>100</v>
       </c>
       <c r="F466">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G466">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H466">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="467">
@@ -14367,13 +14367,13 @@
         <v>100</v>
       </c>
       <c r="F467">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G467">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H467">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="468">
@@ -14397,13 +14397,13 @@
         <v>100</v>
       </c>
       <c r="F468">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G468">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H468">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="469">
@@ -14427,13 +14427,13 @@
         <v>100</v>
       </c>
       <c r="F469">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G469">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H469">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="470">
@@ -14457,13 +14457,13 @@
         <v>100</v>
       </c>
       <c r="F470">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G470">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H470">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="471">
@@ -14487,13 +14487,13 @@
         <v>100</v>
       </c>
       <c r="F471">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G471">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H471">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="472">
@@ -14517,13 +14517,13 @@
         <v>100</v>
       </c>
       <c r="F472">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G472">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H472">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="473">
@@ -14547,13 +14547,13 @@
         <v>100</v>
       </c>
       <c r="F473">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G473">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H473">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="474">
@@ -14577,13 +14577,13 @@
         <v>100</v>
       </c>
       <c r="F474">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G474">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H474">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="475">
@@ -14607,13 +14607,13 @@
         <v>100</v>
       </c>
       <c r="F475">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G475">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H475">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="476">
@@ -14637,13 +14637,13 @@
         <v>100</v>
       </c>
       <c r="F476">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G476">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H476">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="477">
@@ -14667,13 +14667,13 @@
         <v>100</v>
       </c>
       <c r="F477">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G477">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H477">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="478">
@@ -14697,13 +14697,13 @@
         <v>100</v>
       </c>
       <c r="F478">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G478">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H478">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="479">
@@ -14727,13 +14727,13 @@
         <v>100</v>
       </c>
       <c r="F479">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G479">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H479">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="480">
@@ -14757,13 +14757,13 @@
         <v>100</v>
       </c>
       <c r="F480">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G480">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H480">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="481">
@@ -14787,13 +14787,13 @@
         <v>100</v>
       </c>
       <c r="F481">
-        <v>315.08</v>
+        <v>153.59</v>
       </c>
       <c r="G481">
-        <v>344.85</v>
+        <v>166.25</v>
       </c>
       <c r="H481">
-        <v>246.25</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="482">
@@ -14817,13 +14817,13 @@
         <v>100</v>
       </c>
       <c r="F482">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G482">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H482">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="483">
@@ -14847,13 +14847,13 @@
         <v>100</v>
       </c>
       <c r="F483">
-        <v>237.71</v>
+        <v>127.68</v>
       </c>
       <c r="G483">
-        <v>289.84</v>
+        <v>150.62</v>
       </c>
       <c r="H483">
-        <v>190.53</v>
+        <v>85.11</v>
       </c>
     </row>
     <row r="484">
@@ -14877,13 +14877,13 @@
         <v>100</v>
       </c>
       <c r="F484">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G484">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H484">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="485">
@@ -14907,13 +14907,13 @@
         <v>100</v>
       </c>
       <c r="F485">
-        <v>206.9</v>
+        <v>82.22</v>
       </c>
       <c r="G485">
-        <v>283.76</v>
+        <v>103.29</v>
       </c>
       <c r="H485">
-        <v>261.09</v>
+        <v>127.69</v>
       </c>
     </row>
     <row r="486">
@@ -14937,13 +14937,13 @@
         <v>100</v>
       </c>
       <c r="F486">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G486">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H486">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="487">
@@ -14967,13 +14967,13 @@
         <v>100</v>
       </c>
       <c r="F487">
-        <v>277.14</v>
+        <v>135.99</v>
       </c>
       <c r="G487">
-        <v>321.75</v>
+        <v>164.7</v>
       </c>
       <c r="H487">
-        <v>224.57</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="488">
@@ -14997,13 +14997,13 @@
         <v>100</v>
       </c>
       <c r="F488">
-        <v>270.8</v>
+        <v>138.49</v>
       </c>
       <c r="G488">
-        <v>316.79</v>
+        <v>167.15</v>
       </c>
       <c r="H488">
-        <v>207.63</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="489">
@@ -15027,13 +15027,13 @@
         <v>100</v>
       </c>
       <c r="F489">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G489">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H489">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="490">
@@ -15057,13 +15057,13 @@
         <v>100</v>
       </c>
       <c r="F490">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G490">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H490">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="491">
@@ -15087,13 +15087,13 @@
         <v>100</v>
       </c>
       <c r="F491">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G491">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H491">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="492">
@@ -15117,13 +15117,13 @@
         <v>100</v>
       </c>
       <c r="F492">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G492">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H492">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="493">
@@ -15147,13 +15147,13 @@
         <v>100</v>
       </c>
       <c r="F493">
-        <v>259.71</v>
+        <v>133.86</v>
       </c>
       <c r="G493">
-        <v>311.48</v>
+        <v>158.18</v>
       </c>
       <c r="H493">
-        <v>214.11</v>
+        <v>101.32</v>
       </c>
     </row>
     <row r="494">
@@ -15177,13 +15177,13 @@
         <v>100</v>
       </c>
       <c r="F494">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G494">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H494">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="495">
@@ -15207,13 +15207,13 @@
         <v>100</v>
       </c>
       <c r="F495">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G495">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H495">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="496">
@@ -15237,13 +15237,13 @@
         <v>100</v>
       </c>
       <c r="F496">
-        <v>332.24</v>
+        <v>160.83</v>
       </c>
       <c r="G496">
-        <v>355.18</v>
+        <v>167.99</v>
       </c>
       <c r="H496">
-        <v>255.75</v>
+        <v>139.15</v>
       </c>
     </row>
     <row r="497">
@@ -15267,13 +15267,13 @@
         <v>100</v>
       </c>
       <c r="F497">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G497">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H497">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
     <row r="498">
@@ -15297,13 +15297,13 @@
         <v>100</v>
       </c>
       <c r="F498">
-        <v>302.59</v>
+        <v>147.56</v>
       </c>
       <c r="G498">
-        <v>343.62</v>
+        <v>184.3</v>
       </c>
       <c r="H498">
-        <v>228.22</v>
+        <v>113.45</v>
       </c>
     </row>
   </sheetData>
